--- a/research/traditional_assets/database/data/finland/finland_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_oilfield_svcs_equip.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08467486899156748</v>
+        <v>0.08454151925358434</v>
       </c>
       <c r="C2">
-        <v>14413.88773320644</v>
+        <v>14307.53741981873</v>
       </c>
       <c r="D2">
-        <v>13385.58773320644</v>
+        <v>13431.66141981873</v>
       </c>
       <c r="E2">
-        <v>-5598.9</v>
+        <v>-5446.476</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>152.424</v>
       </c>
       <c r="G2">
         <v>1028.3</v>
@@ -1457,28 +1457,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>7.6669272</v>
       </c>
       <c r="N2">
-        <v>364.9265306122447</v>
+        <v>357.2596034122448</v>
       </c>
       <c r="O2">
-        <v>72.98530612244895</v>
+        <v>71.45192068244896</v>
       </c>
       <c r="P2">
-        <v>291.9412244897958</v>
+        <v>285.8076827297958</v>
       </c>
       <c r="Q2">
-        <v>1388.341224489796</v>
+        <v>1382.207682729796</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08467486899156748</v>
+        <v>0.08498900934705489</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8057672793224576</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>47.59749520149934</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08454151925358434</v>
+        <v>0.08440816951560121</v>
       </c>
       <c r="C3">
-        <v>14307.53741981873</v>
+        <v>14201.50537658548</v>
       </c>
       <c r="D3">
-        <v>13431.66141981873</v>
+        <v>13478.05337658548</v>
       </c>
       <c r="E3">
-        <v>-5446.476</v>
+        <v>-5294.052</v>
       </c>
       <c r="F3">
-        <v>152.424</v>
+        <v>304.848</v>
       </c>
       <c r="G3">
         <v>1028.3</v>
@@ -1539,28 +1539,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M3">
-        <v>7.6669272</v>
+        <v>15.3338544</v>
       </c>
       <c r="N3">
-        <v>357.2596034122448</v>
+        <v>349.5926762122447</v>
       </c>
       <c r="O3">
-        <v>71.45192068244896</v>
+        <v>69.91853524244895</v>
       </c>
       <c r="P3">
-        <v>285.8076827297958</v>
+        <v>279.6741409697958</v>
       </c>
       <c r="Q3">
-        <v>1382.207682729796</v>
+        <v>1376.074140969796</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08498900934705489</v>
+        <v>0.08530956073020532</v>
       </c>
       <c r="T3">
-        <v>0.8057672793224576</v>
+        <v>0.8123581531462067</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>47.59749520149934</v>
+        <v>23.79874760074967</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08440816951560121</v>
+        <v>0.08427481977761807</v>
       </c>
       <c r="C4">
-        <v>14201.50537658548</v>
+        <v>14095.7949127808</v>
       </c>
       <c r="D4">
-        <v>13478.05337658548</v>
+        <v>13524.7669127808</v>
       </c>
       <c r="E4">
-        <v>-5294.052</v>
+        <v>-5141.628</v>
       </c>
       <c r="F4">
-        <v>304.848</v>
+        <v>457.272</v>
       </c>
       <c r="G4">
         <v>1028.3</v>
@@ -1621,28 +1621,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M4">
-        <v>15.3338544</v>
+        <v>23.0007816</v>
       </c>
       <c r="N4">
-        <v>349.5926762122447</v>
+        <v>341.9257490122448</v>
       </c>
       <c r="O4">
-        <v>69.91853524244895</v>
+        <v>68.38514980244895</v>
       </c>
       <c r="P4">
-        <v>279.6741409697958</v>
+        <v>273.5405992097958</v>
       </c>
       <c r="Q4">
-        <v>1376.074140969796</v>
+        <v>1369.940599209796</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08530956073020532</v>
+        <v>0.08563672142022481</v>
       </c>
       <c r="T4">
-        <v>0.8123581531462067</v>
+        <v>0.8190849212756002</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>23.79874760074967</v>
+        <v>15.86583173383311</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08427481977761807</v>
+        <v>0.08414147003963494</v>
       </c>
       <c r="C5">
-        <v>14095.7949127808</v>
+        <v>13990.40938371678</v>
       </c>
       <c r="D5">
-        <v>13524.7669127808</v>
+        <v>13571.80538371678</v>
       </c>
       <c r="E5">
-        <v>-5141.628</v>
+        <v>-4989.204</v>
       </c>
       <c r="F5">
-        <v>457.272</v>
+        <v>609.696</v>
       </c>
       <c r="G5">
         <v>1028.3</v>
@@ -1703,28 +1703,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M5">
-        <v>23.0007816</v>
+        <v>30.6677088</v>
       </c>
       <c r="N5">
-        <v>341.9257490122448</v>
+        <v>334.2588218122447</v>
       </c>
       <c r="O5">
-        <v>68.38514980244895</v>
+        <v>66.85176436244895</v>
       </c>
       <c r="P5">
-        <v>273.5405992097958</v>
+        <v>267.4070574497958</v>
       </c>
       <c r="Q5">
-        <v>1369.940599209796</v>
+        <v>1363.807057449796</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08563672142022481</v>
+        <v>0.08597069795795306</v>
       </c>
       <c r="T5">
-        <v>0.8190849212756002</v>
+        <v>0.8259518304076895</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>15.86583173383311</v>
+        <v>11.89937380037483</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08414147003963494</v>
+        <v>0.08400812030165179</v>
       </c>
       <c r="C6">
-        <v>13990.40938371678</v>
+        <v>13885.35219154686</v>
       </c>
       <c r="D6">
-        <v>13571.80538371678</v>
+        <v>13619.17219154686</v>
       </c>
       <c r="E6">
-        <v>-4989.204</v>
+        <v>-4836.78</v>
       </c>
       <c r="F6">
-        <v>609.696</v>
+        <v>762.12</v>
       </c>
       <c r="G6">
         <v>1028.3</v>
@@ -1785,28 +1785,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M6">
-        <v>30.6677088</v>
+        <v>38.334636</v>
       </c>
       <c r="N6">
-        <v>334.2588218122447</v>
+        <v>326.5918946122447</v>
       </c>
       <c r="O6">
-        <v>66.85176436244895</v>
+        <v>65.31837892244896</v>
       </c>
       <c r="P6">
-        <v>267.4070574497958</v>
+        <v>261.2735156897958</v>
       </c>
       <c r="Q6">
-        <v>1363.807057449796</v>
+        <v>1357.673515689796</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08597069795795306</v>
+        <v>0.0863117055806861</v>
       </c>
       <c r="T6">
-        <v>0.8259518304076895</v>
+        <v>0.8329633060478225</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>11.89937380037483</v>
+        <v>9.519499040299868</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08400812030165179</v>
+        <v>0.08394677056366866</v>
       </c>
       <c r="C7">
-        <v>13885.35219154686</v>
+        <v>13754.83129456587</v>
       </c>
       <c r="D7">
-        <v>13619.17219154686</v>
+        <v>13641.07529456587</v>
       </c>
       <c r="E7">
-        <v>-4836.78</v>
+        <v>-4684.356</v>
       </c>
       <c r="F7">
-        <v>762.12</v>
+        <v>914.5440000000001</v>
       </c>
       <c r="G7">
         <v>1028.3</v>
@@ -1867,45 +1867,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M7">
-        <v>38.334636</v>
+        <v>47.3733792</v>
       </c>
       <c r="N7">
-        <v>326.5918946122447</v>
+        <v>317.5531514122447</v>
       </c>
       <c r="O7">
-        <v>65.31837892244896</v>
+        <v>63.51063028244895</v>
       </c>
       <c r="P7">
-        <v>261.2735156897958</v>
+        <v>254.0425211297958</v>
       </c>
       <c r="Q7">
-        <v>1357.673515689796</v>
+        <v>1350.442521129796</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0863117055806861</v>
+        <v>0.0866599686847539</v>
       </c>
       <c r="T7">
-        <v>0.8329633060478225</v>
+        <v>0.8401239620207247</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>9.519499040299868</v>
+        <v>7.703198225982678</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08394677056366866</v>
+        <v>0.08392062082568555</v>
       </c>
       <c r="C8">
-        <v>13754.83129456587</v>
+        <v>13611.76471155003</v>
       </c>
       <c r="D8">
-        <v>13641.07529456587</v>
+        <v>13650.43271155003</v>
       </c>
       <c r="E8">
-        <v>-4684.356</v>
+        <v>-4531.932</v>
       </c>
       <c r="F8">
-        <v>914.544</v>
+        <v>1066.968</v>
       </c>
       <c r="G8">
         <v>1028.3</v>
@@ -1949,45 +1949,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M8">
-        <v>47.3733792</v>
+        <v>57.08278799999999</v>
       </c>
       <c r="N8">
-        <v>317.5531514122447</v>
+        <v>307.8437426122447</v>
       </c>
       <c r="O8">
-        <v>63.51063028244895</v>
+        <v>61.56874852244895</v>
       </c>
       <c r="P8">
-        <v>254.0425211297958</v>
+        <v>246.2749940897958</v>
       </c>
       <c r="Q8">
-        <v>1350.442521129796</v>
+        <v>1342.674994089796</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0866599686847539</v>
+        <v>0.08701572131794144</v>
       </c>
       <c r="T8">
-        <v>0.8401239620207247</v>
+        <v>0.8474386105951944</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>7.70319822598268</v>
+        <v>6.392934602497776</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08392062082568554</v>
+        <v>0.0838128710877024</v>
       </c>
       <c r="C9">
-        <v>13611.76471155003</v>
+        <v>13498.03367280078</v>
       </c>
       <c r="D9">
-        <v>13650.43271155003</v>
+        <v>13689.12567280078</v>
       </c>
       <c r="E9">
-        <v>-4531.932</v>
+        <v>-4379.508</v>
       </c>
       <c r="F9">
-        <v>1066.968</v>
+        <v>1219.392</v>
       </c>
       <c r="G9">
         <v>1028.3</v>
@@ -2031,28 +2031,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M9">
-        <v>57.082788</v>
+        <v>65.237472</v>
       </c>
       <c r="N9">
-        <v>307.8437426122447</v>
+        <v>299.6890586122447</v>
       </c>
       <c r="O9">
-        <v>61.56874852244895</v>
+        <v>59.93781172244894</v>
       </c>
       <c r="P9">
-        <v>246.2749940897958</v>
+        <v>239.7512468897958</v>
       </c>
       <c r="Q9">
-        <v>1342.674994089796</v>
+        <v>1336.151246889796</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08701572131794144</v>
+        <v>0.08737920770402435</v>
       </c>
       <c r="T9">
-        <v>0.8474386105951944</v>
+        <v>0.8549122732691091</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>6.392934602497775</v>
+        <v>5.593817777185553</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0838128710877024</v>
+        <v>0.08376272134971927</v>
       </c>
       <c r="C10">
-        <v>13498.03367280078</v>
+        <v>13363.69336230725</v>
       </c>
       <c r="D10">
-        <v>13689.12567280078</v>
+        <v>13707.20936230725</v>
       </c>
       <c r="E10">
-        <v>-4379.508</v>
+        <v>-4227.084</v>
       </c>
       <c r="F10">
-        <v>1219.392</v>
+        <v>1371.816</v>
       </c>
       <c r="G10">
         <v>1028.3</v>
@@ -2113,45 +2113,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M10">
-        <v>65.237472</v>
+        <v>74.48960879999998</v>
       </c>
       <c r="N10">
-        <v>299.6890586122447</v>
+        <v>290.4369218122447</v>
       </c>
       <c r="O10">
-        <v>59.93781172244894</v>
+        <v>58.08738436244895</v>
       </c>
       <c r="P10">
-        <v>239.7512468897958</v>
+        <v>232.3495374497958</v>
       </c>
       <c r="Q10">
-        <v>1336.151246889796</v>
+        <v>1328.749537449796</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08737920770402435</v>
+        <v>0.0877506828018893</v>
       </c>
       <c r="T10">
-        <v>0.8549122732691091</v>
+        <v>0.8625501922655274</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>5.593817777185553</v>
+        <v>4.89902600498346</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08376272134971927</v>
+        <v>0.08366137161173612</v>
       </c>
       <c r="C11">
-        <v>13363.69336230725</v>
+        <v>13247.96169589718</v>
       </c>
       <c r="D11">
-        <v>13707.20936230725</v>
+        <v>13743.90169589718</v>
       </c>
       <c r="E11">
-        <v>-4227.084</v>
+        <v>-4074.66</v>
       </c>
       <c r="F11">
-        <v>1371.816</v>
+        <v>1524.24</v>
       </c>
       <c r="G11">
         <v>1028.3</v>
@@ -2195,28 +2195,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M11">
-        <v>74.48960879999998</v>
+        <v>82.76623199999999</v>
       </c>
       <c r="N11">
-        <v>290.4369218122447</v>
+        <v>282.1602986122447</v>
       </c>
       <c r="O11">
-        <v>58.08738436244895</v>
+        <v>56.43205972244895</v>
       </c>
       <c r="P11">
-        <v>232.3495374497958</v>
+        <v>225.7282388897958</v>
       </c>
       <c r="Q11">
-        <v>1328.749537449796</v>
+        <v>1322.128238889796</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0877506828018893</v>
+        <v>0.08813041290192902</v>
       </c>
       <c r="T11">
-        <v>0.8625501922655274</v>
+        <v>0.8703578427951996</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>4.89902600498346</v>
+        <v>4.409123404485114</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08366137161173613</v>
+        <v>0.083648021873753</v>
       </c>
       <c r="C12">
-        <v>13247.96169589717</v>
+        <v>13100.3854389871</v>
       </c>
       <c r="D12">
-        <v>13743.90169589717</v>
+        <v>13748.7494389871</v>
       </c>
       <c r="E12">
-        <v>-4074.66</v>
+        <v>-3922.236</v>
       </c>
       <c r="F12">
-        <v>1524.24</v>
+        <v>1676.664</v>
       </c>
       <c r="G12">
         <v>1028.3</v>
@@ -2277,45 +2277,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M12">
-        <v>82.766232</v>
+        <v>92.71951920000001</v>
       </c>
       <c r="N12">
-        <v>282.1602986122447</v>
+        <v>272.2070114122447</v>
       </c>
       <c r="O12">
-        <v>56.43205972244895</v>
+        <v>54.44140228244894</v>
       </c>
       <c r="P12">
-        <v>225.7282388897958</v>
+        <v>217.7656091297958</v>
       </c>
       <c r="Q12">
-        <v>1322.128238889796</v>
+        <v>1314.165609129796</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08813041290192904</v>
+        <v>0.08851867626264381</v>
       </c>
       <c r="T12">
-        <v>0.8703578427951998</v>
+        <v>0.8783409461457632</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.409123404485113</v>
+        <v>3.935811291526247</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.083648021873753</v>
+        <v>0.08355467213576986</v>
       </c>
       <c r="C13">
-        <v>13100.3854389871</v>
+        <v>12981.95569943545</v>
       </c>
       <c r="D13">
-        <v>13748.7494389871</v>
+        <v>13782.74369943545</v>
       </c>
       <c r="E13">
-        <v>-3922.236</v>
+        <v>-3769.812</v>
       </c>
       <c r="F13">
-        <v>1676.664</v>
+        <v>1829.088</v>
       </c>
       <c r="G13">
         <v>1028.3</v>
@@ -2359,28 +2359,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M13">
-        <v>92.71951920000001</v>
+        <v>101.1485664</v>
       </c>
       <c r="N13">
-        <v>272.2070114122447</v>
+        <v>263.7779642122447</v>
       </c>
       <c r="O13">
-        <v>54.44140228244894</v>
+        <v>52.75559284244895</v>
       </c>
       <c r="P13">
-        <v>217.7656091297958</v>
+        <v>211.0223713697958</v>
       </c>
       <c r="Q13">
-        <v>1314.165609129796</v>
+        <v>1307.422371369796</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08851867626264381</v>
+        <v>0.08891576379064757</v>
       </c>
       <c r="T13">
-        <v>0.8783409461457632</v>
+        <v>0.8865054836633852</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>3.935811291526247</v>
+        <v>3.607827017232394</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08355467213576986</v>
+        <v>0.08346132239778672</v>
       </c>
       <c r="C14">
-        <v>12981.95569943545</v>
+        <v>12863.69448053595</v>
       </c>
       <c r="D14">
-        <v>13782.74369943545</v>
+        <v>13816.90648053595</v>
       </c>
       <c r="E14">
-        <v>-3769.812</v>
+        <v>-3617.388</v>
       </c>
       <c r="F14">
-        <v>1829.088</v>
+        <v>1981.512</v>
       </c>
       <c r="G14">
         <v>1028.3</v>
@@ -2441,28 +2441,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M14">
-        <v>101.1485664</v>
+        <v>109.5776136</v>
       </c>
       <c r="N14">
-        <v>263.7779642122447</v>
+        <v>255.3489170122447</v>
       </c>
       <c r="O14">
-        <v>52.75559284244895</v>
+        <v>51.06978340244895</v>
       </c>
       <c r="P14">
-        <v>211.0223713697958</v>
+        <v>204.2791336097958</v>
       </c>
       <c r="Q14">
-        <v>1307.422371369796</v>
+        <v>1300.679133609796</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08891576379064757</v>
+        <v>0.08932197976757095</v>
       </c>
       <c r="T14">
-        <v>0.8865054836633852</v>
+        <v>0.8948577116986535</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>3.607827017232394</v>
+        <v>3.330301862060671</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08346132239778672</v>
+        <v>0.08336797265980359</v>
       </c>
       <c r="C15">
-        <v>12863.69448053595</v>
+        <v>12745.60303852026</v>
       </c>
       <c r="D15">
-        <v>13816.90648053595</v>
+        <v>13851.23903852026</v>
       </c>
       <c r="E15">
-        <v>-3617.388</v>
+        <v>-3464.963999999999</v>
       </c>
       <c r="F15">
-        <v>1981.512</v>
+        <v>2133.936</v>
       </c>
       <c r="G15">
         <v>1028.3</v>
@@ -2523,28 +2523,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M15">
-        <v>109.5776136</v>
+        <v>118.0066608</v>
       </c>
       <c r="N15">
-        <v>255.3489170122447</v>
+        <v>246.9198698122447</v>
       </c>
       <c r="O15">
-        <v>51.06978340244895</v>
+        <v>49.38397396244895</v>
       </c>
       <c r="P15">
-        <v>204.2791336097958</v>
+        <v>197.5358958497958</v>
       </c>
       <c r="Q15">
-        <v>1300.679133609796</v>
+        <v>1293.935895849796</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08932197976757095</v>
+        <v>0.0897376426276786</v>
       </c>
       <c r="T15">
-        <v>0.8948577116986535</v>
+        <v>0.9034041775952073</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>3.330301862060671</v>
+        <v>3.092423157627766</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08336797265980359</v>
+        <v>0.08357462292182045</v>
       </c>
       <c r="C16">
-        <v>12745.60303852026</v>
+        <v>12517.40429994795</v>
       </c>
       <c r="D16">
-        <v>13851.23903852026</v>
+        <v>13775.46429994795</v>
       </c>
       <c r="E16">
-        <v>-3464.963999999999</v>
+        <v>-3312.54</v>
       </c>
       <c r="F16">
-        <v>2133.936</v>
+        <v>2286.36</v>
       </c>
       <c r="G16">
         <v>1028.3</v>
@@ -2605,45 +2605,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M16">
-        <v>118.0066608</v>
+        <v>132.151608</v>
       </c>
       <c r="N16">
-        <v>246.9198698122447</v>
+        <v>232.7749226122447</v>
       </c>
       <c r="O16">
-        <v>49.38397396244895</v>
+        <v>46.55498452244895</v>
       </c>
       <c r="P16">
-        <v>197.5358958497958</v>
+        <v>186.2199380897958</v>
       </c>
       <c r="Q16">
-        <v>1293.935895849796</v>
+        <v>1282.619938089796</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0897376426276786</v>
+        <v>0.090163085790377</v>
       </c>
       <c r="T16">
-        <v>0.9034041775952073</v>
+        <v>0.9121517368069739</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.092423157627766</v>
+        <v>2.761423308691368</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08357462292182045</v>
+        <v>0.08350127318383731</v>
       </c>
       <c r="C17">
-        <v>12517.40429994795</v>
+        <v>12391.78116399491</v>
       </c>
       <c r="D17">
-        <v>13775.46429994795</v>
+        <v>13802.26516399491</v>
       </c>
       <c r="E17">
-        <v>-3312.54</v>
+        <v>-3160.116</v>
       </c>
       <c r="F17">
-        <v>2286.36</v>
+        <v>2438.784</v>
       </c>
       <c r="G17">
         <v>1028.3</v>
@@ -2687,28 +2687,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M17">
-        <v>132.151608</v>
+        <v>140.9617152</v>
       </c>
       <c r="N17">
-        <v>232.7749226122448</v>
+        <v>223.9648154122447</v>
       </c>
       <c r="O17">
-        <v>46.55498452244895</v>
+        <v>44.79296308244895</v>
       </c>
       <c r="P17">
-        <v>186.2199380897958</v>
+        <v>179.1718523297958</v>
       </c>
       <c r="Q17">
-        <v>1282.619938089796</v>
+        <v>1275.571852329796</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.090163085790377</v>
+        <v>0.09059865855218728</v>
       </c>
       <c r="T17">
-        <v>0.9121517368069739</v>
+        <v>0.9211075712380683</v>
       </c>
       <c r="U17">
         <v>0.0578</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.761423308691369</v>
+        <v>2.588834351898158</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08350127318383731</v>
+        <v>0.08390392344585419</v>
       </c>
       <c r="C18">
-        <v>12391.78116399491</v>
+        <v>12093.5064173492</v>
       </c>
       <c r="D18">
-        <v>13802.26516399491</v>
+        <v>13656.4144173492</v>
       </c>
       <c r="E18">
-        <v>-3160.116</v>
+        <v>-3007.692</v>
       </c>
       <c r="F18">
-        <v>2438.784</v>
+        <v>2591.208</v>
       </c>
       <c r="G18">
         <v>1028.3</v>
@@ -2769,45 +2769,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M18">
-        <v>140.9617152</v>
+        <v>158.8410504</v>
       </c>
       <c r="N18">
-        <v>223.9648154122447</v>
+        <v>206.0854802122447</v>
       </c>
       <c r="O18">
-        <v>44.79296308244895</v>
+        <v>41.21709604244895</v>
       </c>
       <c r="P18">
-        <v>179.1718523297958</v>
+        <v>164.8683841697958</v>
       </c>
       <c r="Q18">
-        <v>1275.571852329796</v>
+        <v>1261.268384169796</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09059865855218728</v>
+        <v>0.09104472704319781</v>
       </c>
       <c r="T18">
-        <v>0.9211075712380683</v>
+        <v>0.9302792089084664</v>
       </c>
       <c r="U18">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.588834351898158</v>
+        <v>2.297432116529524</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08390392344585419</v>
+        <v>0.08426177370787105</v>
       </c>
       <c r="C19">
-        <v>12093.5064173492</v>
+        <v>11814.02245608539</v>
       </c>
       <c r="D19">
-        <v>13656.4144173492</v>
+        <v>13529.35445608539</v>
       </c>
       <c r="E19">
-        <v>-3007.692</v>
+        <v>-2855.268</v>
       </c>
       <c r="F19">
-        <v>2591.208</v>
+        <v>2743.632</v>
       </c>
       <c r="G19">
         <v>1028.3</v>
@@ -2851,45 +2851,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M19">
-        <v>158.8410504</v>
+        <v>175.8668112</v>
       </c>
       <c r="N19">
-        <v>206.0854802122447</v>
+        <v>189.0597194122447</v>
       </c>
       <c r="O19">
-        <v>41.21709604244895</v>
+        <v>37.81194388244894</v>
       </c>
       <c r="P19">
-        <v>164.8683841697958</v>
+        <v>151.2477755297958</v>
       </c>
       <c r="Q19">
-        <v>1261.268384169796</v>
+        <v>1247.647775529796</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09104472704319781</v>
+        <v>0.09150167525350128</v>
       </c>
       <c r="T19">
-        <v>0.9302792089084664</v>
+        <v>0.9396745450586302</v>
       </c>
       <c r="U19">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.297432116529524</v>
+        <v>2.075016474809686</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08426177370787105</v>
+        <v>0.08542442396988792</v>
       </c>
       <c r="C20">
-        <v>11814.02245608539</v>
+        <v>11264.62341071336</v>
       </c>
       <c r="D20">
-        <v>13529.35445608539</v>
+        <v>13132.37941071337</v>
       </c>
       <c r="E20">
-        <v>-2855.268</v>
+        <v>-2702.844</v>
       </c>
       <c r="F20">
-        <v>2743.632</v>
+        <v>2896.056</v>
       </c>
       <c r="G20">
         <v>1028.3</v>
@@ -2933,45 +2933,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M20">
-        <v>175.8668112</v>
+        <v>208.2264264</v>
       </c>
       <c r="N20">
-        <v>189.0597194122448</v>
+        <v>156.7001042122447</v>
       </c>
       <c r="O20">
-        <v>37.81194388244895</v>
+        <v>31.34002084244895</v>
       </c>
       <c r="P20">
-        <v>151.2477755297958</v>
+        <v>125.3600833697958</v>
       </c>
       <c r="Q20">
-        <v>1247.647775529796</v>
+        <v>1221.760083369796</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09150167525350128</v>
+        <v>0.0919699061356641</v>
       </c>
       <c r="T20">
-        <v>0.9396745450586301</v>
+        <v>0.9493018648174401</v>
       </c>
       <c r="U20">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.075016474809687</v>
+        <v>1.752546672011871</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08542442396988792</v>
+        <v>0.08608787423190478</v>
       </c>
       <c r="C21">
-        <v>11264.62341071336</v>
+        <v>10895.93879316897</v>
       </c>
       <c r="D21">
-        <v>13132.37941071337</v>
+        <v>12916.11879316897</v>
       </c>
       <c r="E21">
-        <v>-2702.844</v>
+        <v>-2550.42</v>
       </c>
       <c r="F21">
-        <v>2896.056</v>
+        <v>3048.48</v>
       </c>
       <c r="G21">
         <v>1028.3</v>
@@ -3015,45 +3015,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M21">
-        <v>208.2264264</v>
+        <v>231.074784</v>
       </c>
       <c r="N21">
-        <v>156.7001042122447</v>
+        <v>133.8517466122447</v>
       </c>
       <c r="O21">
-        <v>31.34002084244895</v>
+        <v>26.77034932244894</v>
       </c>
       <c r="P21">
-        <v>125.3600833697958</v>
+        <v>107.0813972897958</v>
       </c>
       <c r="Q21">
-        <v>1221.760083369796</v>
+        <v>1203.481397289796</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0919699061356641</v>
+        <v>0.09244984278988097</v>
       </c>
       <c r="T21">
-        <v>0.9493018648174401</v>
+        <v>0.9591698675702199</v>
       </c>
       <c r="U21">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.752546672011871</v>
+        <v>1.57925726163286</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08608787423190478</v>
+        <v>0.08615852449392165</v>
       </c>
       <c r="C22">
-        <v>10895.93879316897</v>
+        <v>10720.9042743648</v>
       </c>
       <c r="D22">
-        <v>12916.11879316897</v>
+        <v>12893.5082743648</v>
       </c>
       <c r="E22">
-        <v>-2550.42</v>
+        <v>-2397.995999999999</v>
       </c>
       <c r="F22">
-        <v>3048.48</v>
+        <v>3200.904</v>
       </c>
       <c r="G22">
         <v>1028.3</v>
@@ -3097,28 +3097,28 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M22">
-        <v>231.074784</v>
+        <v>242.6285232</v>
       </c>
       <c r="N22">
-        <v>133.8517466122447</v>
+        <v>122.2980074122447</v>
       </c>
       <c r="O22">
-        <v>26.77034932244894</v>
+        <v>24.45960148244894</v>
       </c>
       <c r="P22">
-        <v>107.0813972897958</v>
+        <v>97.83840592979575</v>
       </c>
       <c r="Q22">
-        <v>1203.481397289796</v>
+        <v>1194.238405929796</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09244984278988097</v>
+        <v>0.09294192973914132</v>
       </c>
       <c r="T22">
-        <v>0.9591698675702199</v>
+        <v>0.9692876931775009</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>1.57925726163286</v>
+        <v>1.504054534888438</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08615852449392165</v>
+        <v>0.09433304287258776</v>
       </c>
       <c r="C23">
-        <v>10720.9042743648</v>
+        <v>8396.800649187018</v>
       </c>
       <c r="D23">
-        <v>12893.5082743648</v>
+        <v>10721.82864918702</v>
       </c>
       <c r="E23">
-        <v>-2397.996</v>
+        <v>-2245.572</v>
       </c>
       <c r="F23">
-        <v>3200.904</v>
+        <v>3353.328</v>
       </c>
       <c r="G23">
         <v>1028.3</v>
@@ -3179,45 +3179,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M23">
-        <v>242.6285232</v>
+        <v>397.7047008</v>
       </c>
       <c r="N23">
-        <v>122.2980074122447</v>
+        <v>-32.77817018775528</v>
       </c>
       <c r="O23">
-        <v>24.45960148244895</v>
+        <v>-6.555634037551056</v>
       </c>
       <c r="P23">
-        <v>97.83840592979577</v>
+        <v>-26.22253615020422</v>
       </c>
       <c r="Q23">
-        <v>1194.238405929796</v>
+        <v>1070.177463849796</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09294192973914132</v>
+        <v>0.09362737293571613</v>
       </c>
       <c r="T23">
-        <v>0.9692876931775009</v>
+        <v>0.9833811267405432</v>
       </c>
       <c r="U23">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V23">
-        <v>0.2</v>
+        <v>0.1835163275053976</v>
       </c>
       <c r="W23">
-        <v>0.06064000000000001</v>
+        <v>0.09683496355785985</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y23">
-        <v>1.504054534888438</v>
+        <v>0.9175816375269877</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09433304287258776</v>
+        <v>0.09506104287258775</v>
       </c>
       <c r="C24">
-        <v>8396.800649187018</v>
+        <v>8085.925045212722</v>
       </c>
       <c r="D24">
-        <v>10721.82864918702</v>
+        <v>10563.37704521272</v>
       </c>
       <c r="E24">
-        <v>-2245.572</v>
+        <v>-2093.148</v>
       </c>
       <c r="F24">
-        <v>3353.328</v>
+        <v>3505.752</v>
       </c>
       <c r="G24">
         <v>1028.3</v>
@@ -3261,37 +3261,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M24">
-        <v>397.7047008</v>
+        <v>415.7821872</v>
       </c>
       <c r="N24">
-        <v>-32.77817018775528</v>
+        <v>-50.85565658775528</v>
       </c>
       <c r="O24">
-        <v>-6.555634037551056</v>
+        <v>-10.17113131755106</v>
       </c>
       <c r="P24">
-        <v>-26.22253615020422</v>
+        <v>-40.68452527020422</v>
       </c>
       <c r="Q24">
-        <v>1070.177463849796</v>
+        <v>1055.715474729796</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09362737293571613</v>
+        <v>0.09424850764916698</v>
       </c>
       <c r="T24">
-        <v>0.9833811267405432</v>
+        <v>0.9961523102047061</v>
       </c>
       <c r="U24">
         <v>0.1186</v>
       </c>
       <c r="V24">
-        <v>0.1835163275053976</v>
+        <v>0.1755373567442933</v>
       </c>
       <c r="W24">
-        <v>0.09683496355785985</v>
+        <v>0.09778126949012683</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.9175816375269877</v>
+        <v>0.8776867837214666</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09506104287258775</v>
+        <v>0.09578904287258776</v>
       </c>
       <c r="C25">
-        <v>8085.925045212722</v>
+        <v>7779.664563315767</v>
       </c>
       <c r="D25">
-        <v>10563.37704521272</v>
+        <v>10409.54056331577</v>
       </c>
       <c r="E25">
-        <v>-2093.148</v>
+        <v>-1940.723999999999</v>
       </c>
       <c r="F25">
-        <v>3505.752</v>
+        <v>3658.176</v>
       </c>
       <c r="G25">
         <v>1028.3</v>
@@ -3343,37 +3343,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M25">
-        <v>415.7821872</v>
+        <v>433.8596736000001</v>
       </c>
       <c r="N25">
-        <v>-50.85565658775528</v>
+        <v>-68.93314298775533</v>
       </c>
       <c r="O25">
-        <v>-10.17113131755106</v>
+        <v>-13.78662859755107</v>
       </c>
       <c r="P25">
-        <v>-40.68452527020422</v>
+        <v>-55.14651439020427</v>
       </c>
       <c r="Q25">
-        <v>1055.715474729796</v>
+        <v>1041.253485609796</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09424850764916698</v>
+        <v>0.09488598801297181</v>
       </c>
       <c r="T25">
-        <v>0.9961523102047061</v>
+        <v>1.009259577444242</v>
       </c>
       <c r="U25">
         <v>0.1186</v>
       </c>
       <c r="V25">
-        <v>0.1755373567442933</v>
+        <v>0.1682233002132811</v>
       </c>
       <c r="W25">
-        <v>0.09778126949012683</v>
+        <v>0.09864871659470487</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.8776867837214666</v>
+        <v>0.8411165010664053</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09578904287258774</v>
+        <v>0.09651704287258775</v>
       </c>
       <c r="C26">
-        <v>7779.664563315771</v>
+        <v>7477.820465043638</v>
       </c>
       <c r="D26">
-        <v>10409.54056331577</v>
+        <v>10260.12046504364</v>
       </c>
       <c r="E26">
-        <v>-1940.724</v>
+        <v>-1788.3</v>
       </c>
       <c r="F26">
-        <v>3658.176</v>
+        <v>3810.6</v>
       </c>
       <c r="G26">
         <v>1028.3</v>
@@ -3425,37 +3425,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M26">
-        <v>433.8596736</v>
+        <v>451.93716</v>
       </c>
       <c r="N26">
-        <v>-68.93314298775528</v>
+        <v>-87.01062938775527</v>
       </c>
       <c r="O26">
-        <v>-13.78662859755106</v>
+        <v>-17.40212587755105</v>
       </c>
       <c r="P26">
-        <v>-55.14651439020422</v>
+        <v>-69.60850351020422</v>
       </c>
       <c r="Q26">
-        <v>1041.253485609796</v>
+        <v>1026.791496489796</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09488598801297181</v>
+        <v>0.09554046785314477</v>
       </c>
       <c r="T26">
-        <v>1.009259577444242</v>
+        <v>1.022716371810165</v>
       </c>
       <c r="U26">
         <v>0.1186</v>
       </c>
       <c r="V26">
-        <v>0.1682233002132811</v>
+        <v>0.1614943682047499</v>
       </c>
       <c r="W26">
-        <v>0.09864871659470487</v>
+        <v>0.09944676793091668</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.8411165010664055</v>
+        <v>0.8074718410237492</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09651704287258775</v>
+        <v>0.1192595448046618</v>
       </c>
       <c r="C27">
-        <v>7477.820465043638</v>
+        <v>4148.943219654628</v>
       </c>
       <c r="D27">
-        <v>10260.12046504364</v>
+        <v>7083.667219654627</v>
       </c>
       <c r="E27">
-        <v>-1788.3</v>
+        <v>-1635.876</v>
       </c>
       <c r="F27">
-        <v>3810.6</v>
+        <v>3963.024</v>
       </c>
       <c r="G27">
         <v>1028.3</v>
@@ -3507,45 +3507,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M27">
-        <v>451.93716</v>
+        <v>795.7752192</v>
       </c>
       <c r="N27">
-        <v>-87.01062938775527</v>
+        <v>-430.8486885877553</v>
       </c>
       <c r="O27">
-        <v>-17.40212587755105</v>
+        <v>-86.16973771755107</v>
       </c>
       <c r="P27">
-        <v>-69.60850351020422</v>
+        <v>-344.6789508702042</v>
       </c>
       <c r="Q27">
-        <v>1026.791496489796</v>
+        <v>751.7210491297958</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09554046785314477</v>
+        <v>0.09708088219180086</v>
       </c>
       <c r="T27">
-        <v>1.022716371810165</v>
+        <v>1.054388911927117</v>
       </c>
       <c r="U27">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1614943682047499</v>
+        <v>0.09171598255575454</v>
       </c>
       <c r="W27">
-        <v>0.09944676793091668</v>
+        <v>0.1823834307028045</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y27">
-        <v>0.8074718410237492</v>
+        <v>0.4585799127787726</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1192595448046618</v>
+        <v>0.1208095448046618</v>
       </c>
       <c r="C28">
-        <v>4148.943219654628</v>
+        <v>3850.142059000505</v>
       </c>
       <c r="D28">
-        <v>7083.667219654627</v>
+        <v>6937.290059000505</v>
       </c>
       <c r="E28">
-        <v>-1635.876</v>
+        <v>-1483.451999999999</v>
       </c>
       <c r="F28">
-        <v>3963.024</v>
+        <v>4115.448</v>
       </c>
       <c r="G28">
         <v>1028.3</v>
@@ -3589,37 +3589,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M28">
-        <v>795.7752192</v>
+        <v>826.3819584000001</v>
       </c>
       <c r="N28">
-        <v>-430.8486885877553</v>
+        <v>-461.4554277877554</v>
       </c>
       <c r="O28">
-        <v>-86.16973771755107</v>
+        <v>-92.29108555755109</v>
       </c>
       <c r="P28">
-        <v>-344.6789508702042</v>
+        <v>-369.1643422302043</v>
       </c>
       <c r="Q28">
-        <v>751.7210491297958</v>
+        <v>727.2356577697958</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09708088219180086</v>
+        <v>0.0977833600300447</v>
       </c>
       <c r="T28">
-        <v>1.054388911927117</v>
+        <v>1.068832595652146</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.09171598255575454</v>
+        <v>0.08831909431294881</v>
       </c>
       <c r="W28">
-        <v>0.1823834307028045</v>
+        <v>0.1830655258619599</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.4585799127787726</v>
+        <v>0.441595471564744</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1208095448046618</v>
+        <v>0.1223595448046618</v>
       </c>
       <c r="C29">
-        <v>3850.142059000505</v>
+        <v>3557.267908481896</v>
       </c>
       <c r="D29">
-        <v>6937.290059000505</v>
+        <v>6796.839908481896</v>
       </c>
       <c r="E29">
-        <v>-1483.451999999999</v>
+        <v>-1331.027999999999</v>
       </c>
       <c r="F29">
-        <v>4115.448</v>
+        <v>4267.872</v>
       </c>
       <c r="G29">
         <v>1028.3</v>
@@ -3671,37 +3671,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M29">
-        <v>826.3819584000001</v>
+        <v>856.9886976000001</v>
       </c>
       <c r="N29">
-        <v>-461.4554277877554</v>
+        <v>-492.0621669877554</v>
       </c>
       <c r="O29">
-        <v>-92.29108555755109</v>
+        <v>-98.41243339755108</v>
       </c>
       <c r="P29">
-        <v>-369.1643422302043</v>
+        <v>-393.6497335902043</v>
       </c>
       <c r="Q29">
-        <v>727.2356577697958</v>
+        <v>702.7502664097958</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0977833600300447</v>
+        <v>0.09850535114157312</v>
       </c>
       <c r="T29">
-        <v>1.068832595652146</v>
+        <v>1.083677492813982</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.08831909431294881</v>
+        <v>0.08516484094462921</v>
       </c>
       <c r="W29">
-        <v>0.1830655258619599</v>
+        <v>0.1836988999383185</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.441595471564744</v>
+        <v>0.425824204723146</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1223595448046618</v>
+        <v>0.1239095448046618</v>
       </c>
       <c r="C30">
-        <v>3557.267908481896</v>
+        <v>3269.967922653359</v>
       </c>
       <c r="D30">
-        <v>6796.839908481896</v>
+        <v>6661.963922653359</v>
       </c>
       <c r="E30">
-        <v>-1331.027999999999</v>
+        <v>-1178.603999999999</v>
       </c>
       <c r="F30">
-        <v>4267.872</v>
+        <v>4420.296</v>
       </c>
       <c r="G30">
         <v>1028.3</v>
@@ -3753,37 +3753,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M30">
-        <v>856.9886976000001</v>
+        <v>887.5954368000001</v>
       </c>
       <c r="N30">
-        <v>-492.0621669877554</v>
+        <v>-522.6689061877554</v>
       </c>
       <c r="O30">
-        <v>-98.41243339755108</v>
+        <v>-104.5337812375511</v>
       </c>
       <c r="P30">
-        <v>-393.6497335902043</v>
+        <v>-418.1351249502043</v>
       </c>
       <c r="Q30">
-        <v>702.7502664097958</v>
+        <v>678.2648750497958</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09850535114157312</v>
+        <v>0.09924768003089104</v>
       </c>
       <c r="T30">
-        <v>1.083677492813982</v>
+        <v>1.098940556093052</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.08516484094462921</v>
+        <v>0.08222812229136613</v>
       </c>
       <c r="W30">
-        <v>0.1836988999383185</v>
+        <v>0.1842885930438937</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.425824204723146</v>
+        <v>0.4111406114568307</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1239095448046618</v>
+        <v>0.1254595448046618</v>
       </c>
       <c r="C31">
-        <v>3269.96792265336</v>
+        <v>2987.916718462907</v>
       </c>
       <c r="D31">
-        <v>6661.963922653359</v>
+        <v>6532.336718462906</v>
       </c>
       <c r="E31">
-        <v>-1178.604</v>
+        <v>-1026.18</v>
       </c>
       <c r="F31">
-        <v>4420.295999999999</v>
+        <v>4572.719999999999</v>
       </c>
       <c r="G31">
         <v>1028.3</v>
@@ -3835,37 +3835,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M31">
-        <v>887.5954367999999</v>
+        <v>918.2021759999999</v>
       </c>
       <c r="N31">
-        <v>-522.6689061877552</v>
+        <v>-553.2756453877552</v>
       </c>
       <c r="O31">
-        <v>-104.533781237551</v>
+        <v>-110.655129077551</v>
       </c>
       <c r="P31">
-        <v>-418.1351249502042</v>
+        <v>-442.6205163102042</v>
       </c>
       <c r="Q31">
-        <v>678.2648750497959</v>
+        <v>653.7794836897959</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09924768003089104</v>
+        <v>0.1000112183170466</v>
       </c>
       <c r="T31">
-        <v>1.098940556093052</v>
+        <v>1.114639706894381</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.08222812229136615</v>
+        <v>0.07948718488165396</v>
       </c>
       <c r="W31">
-        <v>0.1842885930438937</v>
+        <v>0.1848389732757639</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.4111406114568308</v>
+        <v>0.3974359244082697</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1254595448046618</v>
+        <v>0.1270095448046618</v>
       </c>
       <c r="C32">
-        <v>2987.916718462907</v>
+        <v>2710.813754457231</v>
       </c>
       <c r="D32">
-        <v>6532.336718462906</v>
+        <v>6407.657754457231</v>
       </c>
       <c r="E32">
-        <v>-1026.18</v>
+        <v>-873.7559999999994</v>
       </c>
       <c r="F32">
-        <v>4572.719999999999</v>
+        <v>4725.144</v>
       </c>
       <c r="G32">
         <v>1028.3</v>
@@ -3917,37 +3917,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M32">
-        <v>918.2021759999999</v>
+        <v>948.8089152000001</v>
       </c>
       <c r="N32">
-        <v>-553.2756453877552</v>
+        <v>-583.8823845877554</v>
       </c>
       <c r="O32">
-        <v>-110.655129077551</v>
+        <v>-116.7764769175511</v>
       </c>
       <c r="P32">
-        <v>-442.6205163102042</v>
+        <v>-467.1059076702043</v>
       </c>
       <c r="Q32">
-        <v>653.7794836897959</v>
+        <v>629.2940923297958</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1000112183170466</v>
+        <v>0.1007968881477285</v>
       </c>
       <c r="T32">
-        <v>1.114639706894381</v>
+        <v>1.130793905545024</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.07948718488165396</v>
+        <v>0.07692308214353606</v>
       </c>
       <c r="W32">
-        <v>0.1848389732757639</v>
+        <v>0.185353845105578</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3974359244082697</v>
+        <v>0.3846154107176802</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1270095448046618</v>
+        <v>0.1285595448046618</v>
       </c>
       <c r="C33">
-        <v>2710.813754457231</v>
+        <v>2438.381004495509</v>
       </c>
       <c r="D33">
-        <v>6407.657754457231</v>
+        <v>6287.649004495509</v>
       </c>
       <c r="E33">
-        <v>-873.7559999999994</v>
+        <v>-721.3319999999994</v>
       </c>
       <c r="F33">
-        <v>4725.144</v>
+        <v>4877.568</v>
       </c>
       <c r="G33">
         <v>1028.3</v>
@@ -3999,37 +3999,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M33">
-        <v>948.8089152000001</v>
+        <v>979.4156544000001</v>
       </c>
       <c r="N33">
-        <v>-583.8823845877554</v>
+        <v>-614.4891237877554</v>
       </c>
       <c r="O33">
-        <v>-116.7764769175511</v>
+        <v>-122.8978247575511</v>
       </c>
       <c r="P33">
-        <v>-467.1059076702043</v>
+        <v>-491.5912990302043</v>
       </c>
       <c r="Q33">
-        <v>629.2940923297958</v>
+        <v>604.8087009697958</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1007968881477285</v>
+        <v>0.1016056659146068</v>
       </c>
       <c r="T33">
-        <v>1.130793905545024</v>
+        <v>1.147423227685393</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.07692308214353606</v>
+        <v>0.07451923582655055</v>
       </c>
       <c r="W33">
-        <v>0.185353845105578</v>
+        <v>0.1858365374460287</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3846154107176802</v>
+        <v>0.3725961791327528</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1285595448046618</v>
+        <v>0.1301095448046618</v>
       </c>
       <c r="C34">
-        <v>2438.381004495509</v>
+        <v>2170.360888070632</v>
       </c>
       <c r="D34">
-        <v>6287.649004495509</v>
+        <v>6172.052888070632</v>
       </c>
       <c r="E34">
-        <v>-721.3319999999994</v>
+        <v>-568.9079999999994</v>
       </c>
       <c r="F34">
-        <v>4877.568</v>
+        <v>5029.992</v>
       </c>
       <c r="G34">
         <v>1028.3</v>
@@ -4081,37 +4081,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M34">
-        <v>979.4156544000001</v>
+        <v>1010.0223936</v>
       </c>
       <c r="N34">
-        <v>-614.4891237877554</v>
+        <v>-645.0958629877554</v>
       </c>
       <c r="O34">
-        <v>-122.8978247575511</v>
+        <v>-129.0191725975511</v>
       </c>
       <c r="P34">
-        <v>-491.5912990302043</v>
+        <v>-516.0766903902042</v>
       </c>
       <c r="Q34">
-        <v>604.8087009697958</v>
+        <v>580.3233096097958</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1016056659146068</v>
+        <v>0.102438586301392</v>
       </c>
       <c r="T34">
-        <v>1.147423227685393</v>
+        <v>1.164548947501592</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.07451923582655055</v>
+        <v>0.07226107716513994</v>
       </c>
       <c r="W34">
-        <v>0.1858365374460287</v>
+        <v>0.1862899757052399</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3725961791327528</v>
+        <v>0.3613053858256997</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1301095448046618</v>
+        <v>0.1316595448046618</v>
       </c>
       <c r="C35">
-        <v>2170.360888070632</v>
+        <v>1906.514424810729</v>
       </c>
       <c r="D35">
-        <v>6172.052888070632</v>
+        <v>6060.630424810729</v>
       </c>
       <c r="E35">
-        <v>-568.9079999999994</v>
+        <v>-416.4839999999995</v>
       </c>
       <c r="F35">
-        <v>5029.992</v>
+        <v>5182.416</v>
       </c>
       <c r="G35">
         <v>1028.3</v>
@@ -4163,37 +4163,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M35">
-        <v>1010.0223936</v>
+        <v>1040.6291328</v>
       </c>
       <c r="N35">
-        <v>-645.0958629877554</v>
+        <v>-675.7026021877552</v>
       </c>
       <c r="O35">
-        <v>-129.0191725975511</v>
+        <v>-135.1405204375511</v>
       </c>
       <c r="P35">
-        <v>-516.0766903902042</v>
+        <v>-540.5620817502042</v>
       </c>
       <c r="Q35">
-        <v>580.3233096097958</v>
+        <v>555.8379182497958</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.102438586301392</v>
+        <v>0.1032967466998979</v>
       </c>
       <c r="T35">
-        <v>1.164548947501592</v>
+        <v>1.182193628524344</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.07226107716513994</v>
+        <v>0.07013575136616525</v>
       </c>
       <c r="W35">
-        <v>0.1862899757052399</v>
+        <v>0.186716741125674</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3613053858256997</v>
+        <v>0.3506787568308262</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1316595448046618</v>
+        <v>0.1332095448046618</v>
       </c>
       <c r="C36">
-        <v>1906.514424810729</v>
+        <v>1646.61958533376</v>
       </c>
       <c r="D36">
-        <v>6060.630424810729</v>
+        <v>5953.15958533376</v>
       </c>
       <c r="E36">
-        <v>-416.4839999999995</v>
+        <v>-264.0599999999995</v>
       </c>
       <c r="F36">
-        <v>5182.416</v>
+        <v>5334.84</v>
       </c>
       <c r="G36">
         <v>1028.3</v>
@@ -4245,37 +4245,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M36">
-        <v>1040.6291328</v>
+        <v>1071.235872</v>
       </c>
       <c r="N36">
-        <v>-675.7026021877552</v>
+        <v>-706.3093413877552</v>
       </c>
       <c r="O36">
-        <v>-135.1405204375511</v>
+        <v>-141.2618682775511</v>
       </c>
       <c r="P36">
-        <v>-540.5620817502042</v>
+        <v>-565.0474731102042</v>
       </c>
       <c r="Q36">
-        <v>555.8379182497958</v>
+        <v>531.3525268897959</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1032967466998979</v>
+        <v>0.1041813120337425</v>
       </c>
       <c r="T36">
-        <v>1.182193628524344</v>
+        <v>1.200381222809334</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.07013575136616525</v>
+        <v>0.06813187275570337</v>
       </c>
       <c r="W36">
-        <v>0.186716741125674</v>
+        <v>0.1871191199506547</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3506787568308262</v>
+        <v>0.3406593637785169</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1332095448046618</v>
+        <v>0.1347595448046618</v>
       </c>
       <c r="C37">
-        <v>1646.61958533376</v>
+        <v>1390.469814506932</v>
       </c>
       <c r="D37">
-        <v>5953.15958533376</v>
+        <v>5849.433814506932</v>
       </c>
       <c r="E37">
-        <v>-264.0599999999995</v>
+        <v>-111.6359999999995</v>
       </c>
       <c r="F37">
-        <v>5334.84</v>
+        <v>5487.264</v>
       </c>
       <c r="G37">
         <v>1028.3</v>
@@ -4327,37 +4327,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M37">
-        <v>1071.235872</v>
+        <v>1101.8426112</v>
       </c>
       <c r="N37">
-        <v>-706.3093413877552</v>
+        <v>-736.9160805877552</v>
       </c>
       <c r="O37">
-        <v>-141.2618682775511</v>
+        <v>-147.3832161175511</v>
       </c>
       <c r="P37">
-        <v>-565.0474731102042</v>
+        <v>-589.5328644702042</v>
       </c>
       <c r="Q37">
-        <v>531.3525268897959</v>
+        <v>506.8671355297959</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1041813120337425</v>
+        <v>0.1050935200342697</v>
       </c>
       <c r="T37">
-        <v>1.200381222809334</v>
+        <v>1.21913717941573</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.06813187275570337</v>
+        <v>0.06623932073471162</v>
       </c>
       <c r="W37">
-        <v>0.1871191199506547</v>
+        <v>0.1874991443964699</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3406593637785169</v>
+        <v>0.3311966036735581</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1347595448046618</v>
+        <v>0.1363095448046618</v>
       </c>
       <c r="C38">
-        <v>1390.469814506933</v>
+        <v>1137.87270644354</v>
       </c>
       <c r="D38">
-        <v>5849.433814506932</v>
+        <v>5749.26070644354</v>
       </c>
       <c r="E38">
-        <v>-111.6360000000004</v>
+        <v>40.78800000000047</v>
       </c>
       <c r="F38">
-        <v>5487.263999999999</v>
+        <v>5639.688</v>
       </c>
       <c r="G38">
         <v>1028.3</v>
@@ -4409,37 +4409,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M38">
-        <v>1101.8426112</v>
+        <v>1132.4493504</v>
       </c>
       <c r="N38">
-        <v>-736.9160805877552</v>
+        <v>-767.5228197877552</v>
       </c>
       <c r="O38">
-        <v>-147.3832161175511</v>
+        <v>-153.5045639575511</v>
       </c>
       <c r="P38">
-        <v>-589.5328644702042</v>
+        <v>-614.0182558302042</v>
       </c>
       <c r="Q38">
-        <v>506.8671355297959</v>
+        <v>482.3817441697959</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1050935200342697</v>
+        <v>0.1060346870189407</v>
       </c>
       <c r="T38">
-        <v>1.21913717941573</v>
+        <v>1.238488563215979</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.06623932073471162</v>
+        <v>0.06444906882296265</v>
       </c>
       <c r="W38">
-        <v>0.1874991443964699</v>
+        <v>0.1878586269803491</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3311966036735581</v>
+        <v>0.3222453441148133</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1363095448046618</v>
+        <v>0.1378595448046618</v>
       </c>
       <c r="C39">
-        <v>1137.87270644354</v>
+        <v>888.648813353735</v>
       </c>
       <c r="D39">
-        <v>5749.26070644354</v>
+        <v>5652.460813353735</v>
       </c>
       <c r="E39">
-        <v>40.78800000000047</v>
+        <v>193.2120000000004</v>
       </c>
       <c r="F39">
-        <v>5639.688</v>
+        <v>5792.112</v>
       </c>
       <c r="G39">
         <v>1028.3</v>
@@ -4491,37 +4491,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M39">
-        <v>1132.4493504</v>
+        <v>1163.0560896</v>
       </c>
       <c r="N39">
-        <v>-767.5228197877552</v>
+        <v>-798.1295589877552</v>
       </c>
       <c r="O39">
-        <v>-153.5045639575511</v>
+        <v>-159.6259117975511</v>
       </c>
       <c r="P39">
-        <v>-614.0182558302042</v>
+        <v>-638.5036471902042</v>
       </c>
       <c r="Q39">
-        <v>482.3817441697959</v>
+        <v>457.8963528097959</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1060346870189407</v>
+        <v>0.1070062142289236</v>
       </c>
       <c r="T39">
-        <v>1.238488563215979</v>
+        <v>1.258464185203334</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.06444906882296265</v>
+        <v>0.06275304069604258</v>
       </c>
       <c r="W39">
-        <v>0.1878586269803491</v>
+        <v>0.1881991894282347</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3222453441148133</v>
+        <v>0.313765203480213</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1378595448046618</v>
+        <v>0.1394095448046618</v>
       </c>
       <c r="C40">
-        <v>888.648813353735</v>
+        <v>642.6305727345652</v>
       </c>
       <c r="D40">
-        <v>5652.460813353735</v>
+        <v>5558.866572734565</v>
       </c>
       <c r="E40">
-        <v>193.2120000000004</v>
+        <v>345.6360000000004</v>
       </c>
       <c r="F40">
-        <v>5792.112</v>
+        <v>5944.536</v>
       </c>
       <c r="G40">
         <v>1028.3</v>
@@ -4573,37 +4573,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M40">
-        <v>1163.0560896</v>
+        <v>1193.6628288</v>
       </c>
       <c r="N40">
-        <v>-798.1295589877552</v>
+        <v>-828.7362981877552</v>
       </c>
       <c r="O40">
-        <v>-159.6259117975511</v>
+        <v>-165.7472596375511</v>
       </c>
       <c r="P40">
-        <v>-638.5036471902042</v>
+        <v>-662.9890385502042</v>
       </c>
       <c r="Q40">
-        <v>457.8963528097959</v>
+        <v>433.4109614497959</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1070062142289236</v>
+        <v>0.1080095947900535</v>
       </c>
       <c r="T40">
-        <v>1.258464185203334</v>
+        <v>1.279094745616503</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.06275304069604258</v>
+        <v>0.06114398837050303</v>
       </c>
       <c r="W40">
-        <v>0.1881991894282347</v>
+        <v>0.188522287135203</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.313765203480213</v>
+        <v>0.3057199418525152</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1394095448046618</v>
+        <v>0.1409595448046618</v>
       </c>
       <c r="C41">
-        <v>642.6305727345652</v>
+        <v>399.6613394064161</v>
       </c>
       <c r="D41">
-        <v>5558.866572734565</v>
+        <v>5468.321339406416</v>
       </c>
       <c r="E41">
-        <v>345.6360000000004</v>
+        <v>498.0600000000004</v>
       </c>
       <c r="F41">
-        <v>5944.536</v>
+        <v>6096.96</v>
       </c>
       <c r="G41">
         <v>1028.3</v>
@@ -4655,37 +4655,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M41">
-        <v>1193.6628288</v>
+        <v>1224.269568</v>
       </c>
       <c r="N41">
-        <v>-828.7362981877552</v>
+        <v>-859.3430373877552</v>
       </c>
       <c r="O41">
-        <v>-165.7472596375511</v>
+        <v>-171.8686074775511</v>
       </c>
       <c r="P41">
-        <v>-662.9890385502042</v>
+        <v>-687.4744299102042</v>
       </c>
       <c r="Q41">
-        <v>433.4109614497959</v>
+        <v>408.9255700897959</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1080095947900535</v>
+        <v>0.1090464213698877</v>
       </c>
       <c r="T41">
-        <v>1.279094745616503</v>
+        <v>1.300412991376778</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.06114398837050303</v>
+        <v>0.05961538866124046</v>
       </c>
       <c r="W41">
-        <v>0.188522287135203</v>
+        <v>0.1888292299568229</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3057199418525152</v>
+        <v>0.2980769433062023</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1409595448046618</v>
+        <v>0.1425095448046618</v>
       </c>
       <c r="C42">
-        <v>399.6613394064161</v>
+        <v>159.5945106328963</v>
       </c>
       <c r="D42">
-        <v>5468.321339406416</v>
+        <v>5380.678510632896</v>
       </c>
       <c r="E42">
-        <v>498.0600000000004</v>
+        <v>650.4840000000004</v>
       </c>
       <c r="F42">
-        <v>6096.96</v>
+        <v>6249.384</v>
       </c>
       <c r="G42">
         <v>1028.3</v>
@@ -4737,37 +4737,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M42">
-        <v>1224.269568</v>
+        <v>1254.8763072</v>
       </c>
       <c r="N42">
-        <v>-859.3430373877552</v>
+        <v>-889.9497765877554</v>
       </c>
       <c r="O42">
-        <v>-171.8686074775511</v>
+        <v>-177.9899553175511</v>
       </c>
       <c r="P42">
-        <v>-687.4744299102042</v>
+        <v>-711.9598212702043</v>
       </c>
       <c r="Q42">
-        <v>408.9255700897959</v>
+        <v>384.4401787297958</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1090464213698877</v>
+        <v>0.1101183946134452</v>
       </c>
       <c r="T42">
-        <v>1.300412991376778</v>
+        <v>1.322453889535707</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.05961538866124046</v>
+        <v>0.0581613547914541</v>
       </c>
       <c r="W42">
-        <v>0.1888292299568229</v>
+        <v>0.189121199957876</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2980769433062023</v>
+        <v>0.2908067739572705</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1425095448046618</v>
+        <v>0.1440595448046618</v>
       </c>
       <c r="C43">
-        <v>159.5945106328963</v>
+        <v>-77.70726595421092</v>
       </c>
       <c r="D43">
-        <v>5380.678510632896</v>
+        <v>5295.80073404579</v>
       </c>
       <c r="E43">
-        <v>650.4840000000004</v>
+        <v>802.9080000000013</v>
       </c>
       <c r="F43">
-        <v>6249.384</v>
+        <v>6401.808000000001</v>
       </c>
       <c r="G43">
         <v>1028.3</v>
@@ -4819,37 +4819,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M43">
-        <v>1254.8763072</v>
+        <v>1285.4830464</v>
       </c>
       <c r="N43">
-        <v>-889.9497765877554</v>
+        <v>-920.5565157877554</v>
       </c>
       <c r="O43">
-        <v>-177.9899553175511</v>
+        <v>-184.1113031575511</v>
       </c>
       <c r="P43">
-        <v>-711.9598212702043</v>
+        <v>-736.4452126302043</v>
       </c>
       <c r="Q43">
-        <v>384.4401787297958</v>
+        <v>359.9547873697958</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1101183946134452</v>
+        <v>0.111227332451608</v>
       </c>
       <c r="T43">
-        <v>1.322453889535707</v>
+        <v>1.345254818665633</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.0581613547914541</v>
+        <v>0.05677656062975281</v>
       </c>
       <c r="W43">
-        <v>0.189121199957876</v>
+        <v>0.1893992666255457</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2908067739572705</v>
+        <v>0.283882803148764</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1440595448046618</v>
+        <v>0.1456095448046618</v>
       </c>
       <c r="C44">
-        <v>-77.70726595421002</v>
+        <v>-312.3728106264743</v>
       </c>
       <c r="D44">
-        <v>5295.80073404579</v>
+        <v>5213.559189373525</v>
       </c>
       <c r="E44">
-        <v>802.9080000000004</v>
+        <v>955.3320000000003</v>
       </c>
       <c r="F44">
-        <v>6401.808</v>
+        <v>6554.232</v>
       </c>
       <c r="G44">
         <v>1028.3</v>
@@ -4901,37 +4901,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M44">
-        <v>1285.4830464</v>
+        <v>1316.0897856</v>
       </c>
       <c r="N44">
-        <v>-920.5565157877554</v>
+        <v>-951.1632549877554</v>
       </c>
       <c r="O44">
-        <v>-184.1113031575511</v>
+        <v>-190.2326509975511</v>
       </c>
       <c r="P44">
-        <v>-736.4452126302043</v>
+        <v>-760.9306039902043</v>
       </c>
       <c r="Q44">
-        <v>359.9547873697958</v>
+        <v>335.4693960097958</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.111227332451608</v>
+        <v>0.1123751803893555</v>
       </c>
       <c r="T44">
-        <v>1.345254818665633</v>
+        <v>1.368855780396609</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.05677656062975281</v>
+        <v>0.05545617549882832</v>
       </c>
       <c r="W44">
-        <v>0.1893992666255457</v>
+        <v>0.1896643999598353</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.283882803148764</v>
+        <v>0.2772808774941417</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1456095448046618</v>
+        <v>0.1471595448046618</v>
       </c>
       <c r="C45">
-        <v>-312.3728106264743</v>
+        <v>-544.523063927064</v>
       </c>
       <c r="D45">
-        <v>5213.559189373525</v>
+        <v>5133.832936072936</v>
       </c>
       <c r="E45">
-        <v>955.3320000000003</v>
+        <v>1107.756</v>
       </c>
       <c r="F45">
-        <v>6554.232</v>
+        <v>6706.656</v>
       </c>
       <c r="G45">
         <v>1028.3</v>
@@ -4983,37 +4983,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M45">
-        <v>1316.0897856</v>
+        <v>1346.6965248</v>
       </c>
       <c r="N45">
-        <v>-951.1632549877554</v>
+        <v>-981.7699941877554</v>
       </c>
       <c r="O45">
-        <v>-190.2326509975511</v>
+        <v>-196.3539988375511</v>
       </c>
       <c r="P45">
-        <v>-760.9306039902043</v>
+        <v>-785.4159953502043</v>
       </c>
       <c r="Q45">
-        <v>335.4693960097958</v>
+        <v>310.9840046497958</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1123751803893555</v>
+        <v>0.1135640228963083</v>
       </c>
       <c r="T45">
-        <v>1.368855780396609</v>
+        <v>1.393299633617977</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.05545617549882832</v>
+        <v>0.05419580787385495</v>
       </c>
       <c r="W45">
-        <v>0.1896643999598353</v>
+        <v>0.1899174817789299</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2772808774941417</v>
+        <v>0.2709790393692748</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1471595448046618</v>
+        <v>0.1487095448046618</v>
       </c>
       <c r="C46">
-        <v>-544.523063927064</v>
+        <v>-774.2716800840735</v>
       </c>
       <c r="D46">
-        <v>5133.832936072936</v>
+        <v>5056.508319915926</v>
       </c>
       <c r="E46">
-        <v>1107.756</v>
+        <v>1260.18</v>
       </c>
       <c r="F46">
-        <v>6706.656</v>
+        <v>6859.08</v>
       </c>
       <c r="G46">
         <v>1028.3</v>
@@ -5065,37 +5065,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M46">
-        <v>1346.6965248</v>
+        <v>1377.303264</v>
       </c>
       <c r="N46">
-        <v>-981.7699941877554</v>
+        <v>-1012.376733387755</v>
       </c>
       <c r="O46">
-        <v>-196.3539988375511</v>
+        <v>-202.4753466775511</v>
       </c>
       <c r="P46">
-        <v>-785.4159953502043</v>
+        <v>-809.9013867102043</v>
       </c>
       <c r="Q46">
-        <v>310.9840046497958</v>
+        <v>286.4986132897958</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1135640228963083</v>
+        <v>0.1147960960398775</v>
       </c>
       <c r="T46">
-        <v>1.393299633617977</v>
+        <v>1.418632354229213</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.05419580787385495</v>
+        <v>0.05299145658776928</v>
       </c>
       <c r="W46">
-        <v>0.1899174817789299</v>
+        <v>0.1901593155171759</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2709790393692748</v>
+        <v>0.2649572829388465</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1487095448046618</v>
+        <v>0.1502595448046618</v>
       </c>
       <c r="C47">
-        <v>-774.2716800840735</v>
+        <v>-1001.725567592446</v>
       </c>
       <c r="D47">
-        <v>5056.508319915926</v>
+        <v>4981.478432407554</v>
       </c>
       <c r="E47">
-        <v>1260.18</v>
+        <v>1412.604</v>
       </c>
       <c r="F47">
-        <v>6859.08</v>
+        <v>7011.504</v>
       </c>
       <c r="G47">
         <v>1028.3</v>
@@ -5147,37 +5147,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M47">
-        <v>1377.303264</v>
+        <v>1407.9100032</v>
       </c>
       <c r="N47">
-        <v>-1012.376733387755</v>
+        <v>-1042.983472587755</v>
       </c>
       <c r="O47">
-        <v>-202.4753466775511</v>
+        <v>-208.5966945175511</v>
       </c>
       <c r="P47">
-        <v>-809.9013867102043</v>
+        <v>-834.3867780702043</v>
       </c>
       <c r="Q47">
-        <v>286.4986132897958</v>
+        <v>262.0132219297958</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1147960960398775</v>
+        <v>0.1160738015220975</v>
       </c>
       <c r="T47">
-        <v>1.418632354229213</v>
+        <v>1.444903323751976</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.05299145658776928</v>
+        <v>0.05183946840107865</v>
       </c>
       <c r="W47">
-        <v>0.1901593155171759</v>
+        <v>0.1903906347450634</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2649572829388465</v>
+        <v>0.2591973420053932</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1502595448046618</v>
+        <v>0.1518095448046618</v>
       </c>
       <c r="C48">
-        <v>-1001.725567592446</v>
+        <v>-1226.98538237176</v>
       </c>
       <c r="D48">
-        <v>4981.478432407554</v>
+        <v>4908.642617628239</v>
       </c>
       <c r="E48">
-        <v>1412.604</v>
+        <v>1565.028</v>
       </c>
       <c r="F48">
-        <v>7011.504</v>
+        <v>7163.928</v>
       </c>
       <c r="G48">
         <v>1028.3</v>
@@ -5229,37 +5229,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M48">
-        <v>1407.9100032</v>
+        <v>1438.5167424</v>
       </c>
       <c r="N48">
-        <v>-1042.983472587755</v>
+        <v>-1073.590211787755</v>
       </c>
       <c r="O48">
-        <v>-208.5966945175511</v>
+        <v>-214.7180423575511</v>
       </c>
       <c r="P48">
-        <v>-834.3867780702043</v>
+        <v>-858.8721694302043</v>
       </c>
       <c r="Q48">
-        <v>262.0132219297958</v>
+        <v>237.5278305697958</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1160738015220975</v>
+        <v>0.1173997223055333</v>
       </c>
       <c r="T48">
-        <v>1.444903323751976</v>
+        <v>1.472165650615221</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.05183946840107865</v>
+        <v>0.05073650098828975</v>
       </c>
       <c r="W48">
-        <v>0.1903906347450634</v>
+        <v>0.1906121106015514</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2591973420053932</v>
+        <v>0.2536825049414487</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1518095448046618</v>
+        <v>0.1533595448046618</v>
       </c>
       <c r="C49">
-        <v>-1226.98538237176</v>
+        <v>-1450.145978283741</v>
       </c>
       <c r="D49">
-        <v>4908.642617628239</v>
+        <v>4837.90602171626</v>
       </c>
       <c r="E49">
-        <v>1565.028</v>
+        <v>1717.452000000001</v>
       </c>
       <c r="F49">
-        <v>7163.928</v>
+        <v>7316.352000000001</v>
       </c>
       <c r="G49">
         <v>1028.3</v>
@@ -5311,37 +5311,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M49">
-        <v>1438.5167424</v>
+        <v>1469.1234816</v>
       </c>
       <c r="N49">
-        <v>-1073.590211787755</v>
+        <v>-1104.196950987755</v>
       </c>
       <c r="O49">
-        <v>-214.7180423575511</v>
+        <v>-220.8393901975511</v>
       </c>
       <c r="P49">
-        <v>-858.8721694302043</v>
+        <v>-883.3575607902043</v>
       </c>
       <c r="Q49">
-        <v>237.5278305697958</v>
+        <v>213.0424392097958</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1173997223055333</v>
+        <v>0.1187766400421781</v>
       </c>
       <c r="T49">
-        <v>1.472165650615221</v>
+        <v>1.500476528511667</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.05073650098828975</v>
+        <v>0.04967949055103371</v>
       </c>
       <c r="W49">
-        <v>0.1906121106015514</v>
+        <v>0.1908243582973524</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2536825049414487</v>
+        <v>0.2483974527551686</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1533595448046618</v>
+        <v>0.1549095448046618</v>
       </c>
       <c r="C50">
-        <v>-1450.145978283739</v>
+        <v>-1671.296819249718</v>
       </c>
       <c r="D50">
-        <v>4837.906021716261</v>
+        <v>4769.179180750281</v>
       </c>
       <c r="E50">
-        <v>1717.452</v>
+        <v>1869.876</v>
       </c>
       <c r="F50">
-        <v>7316.352</v>
+        <v>7468.776</v>
       </c>
       <c r="G50">
         <v>1028.3</v>
@@ -5393,37 +5393,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M50">
-        <v>1469.1234816</v>
+        <v>1499.7302208</v>
       </c>
       <c r="N50">
-        <v>-1104.196950987755</v>
+        <v>-1134.803690187755</v>
       </c>
       <c r="O50">
-        <v>-220.8393901975511</v>
+        <v>-226.9607380375511</v>
       </c>
       <c r="P50">
-        <v>-883.3575607902043</v>
+        <v>-907.8429521502043</v>
       </c>
       <c r="Q50">
-        <v>213.0424392097958</v>
+        <v>188.5570478497958</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1187766400421781</v>
+        <v>0.1202075545528091</v>
       </c>
       <c r="T50">
-        <v>1.500476528511667</v>
+        <v>1.529897636913857</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.04967949055103371</v>
+        <v>0.04866562339693098</v>
       </c>
       <c r="W50">
-        <v>0.1908243582973524</v>
+        <v>0.1910279428218963</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2483974527551686</v>
+        <v>0.2433281169846548</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1549095448046618</v>
+        <v>0.1564595448046618</v>
       </c>
       <c r="C51">
-        <v>-1671.296819249718</v>
+        <v>-1890.522356733101</v>
       </c>
       <c r="D51">
-        <v>4769.179180750281</v>
+        <v>4702.377643266898</v>
       </c>
       <c r="E51">
-        <v>1869.876</v>
+        <v>2022.3</v>
       </c>
       <c r="F51">
-        <v>7468.776</v>
+        <v>7621.2</v>
       </c>
       <c r="G51">
         <v>1028.3</v>
@@ -5475,37 +5475,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M51">
-        <v>1499.7302208</v>
+        <v>1530.33696</v>
       </c>
       <c r="N51">
-        <v>-1134.803690187755</v>
+        <v>-1165.410429387755</v>
       </c>
       <c r="O51">
-        <v>-226.9607380375511</v>
+        <v>-233.0820858775511</v>
       </c>
       <c r="P51">
-        <v>-907.8429521502043</v>
+        <v>-932.3283435102043</v>
       </c>
       <c r="Q51">
-        <v>188.5570478497958</v>
+        <v>164.0716564897958</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1202075545528091</v>
+        <v>0.1216957056438653</v>
       </c>
       <c r="T51">
-        <v>1.529897636913857</v>
+        <v>1.560495589652134</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.04866562339693098</v>
+        <v>0.04769231092899236</v>
       </c>
       <c r="W51">
-        <v>0.1910279428218963</v>
+        <v>0.1912233839654583</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2433281169846548</v>
+        <v>0.2384615546449618</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1564595448046618</v>
+        <v>0.1580095448046618</v>
       </c>
       <c r="C52">
-        <v>-1890.522356733101</v>
+        <v>-2107.902375935853</v>
       </c>
       <c r="D52">
-        <v>4702.377643266898</v>
+        <v>4637.421624064146</v>
       </c>
       <c r="E52">
-        <v>2022.3</v>
+        <v>2174.724</v>
       </c>
       <c r="F52">
-        <v>7621.2</v>
+        <v>7773.624</v>
       </c>
       <c r="G52">
         <v>1028.3</v>
@@ -5557,37 +5557,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M52">
-        <v>1530.33696</v>
+        <v>1560.9436992</v>
       </c>
       <c r="N52">
-        <v>-1165.410429387755</v>
+        <v>-1196.017168587755</v>
       </c>
       <c r="O52">
-        <v>-233.0820858775511</v>
+        <v>-239.2034337175511</v>
       </c>
       <c r="P52">
-        <v>-932.3283435102043</v>
+        <v>-956.8137348702043</v>
       </c>
       <c r="Q52">
-        <v>164.0716564897958</v>
+        <v>139.5862651297958</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1216957056438653</v>
+        <v>0.1232445975957809</v>
       </c>
       <c r="T52">
-        <v>1.560495589652134</v>
+        <v>1.592342438420545</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.04769231092899236</v>
+        <v>0.04675716757744349</v>
       </c>
       <c r="W52">
-        <v>0.1912233839654583</v>
+        <v>0.1914111607504493</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2384615546449618</v>
+        <v>0.2337858378872174</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1580095448046618</v>
+        <v>0.1595595448046618</v>
       </c>
       <c r="C53">
-        <v>-2107.902375935853</v>
+        <v>-2323.512313692921</v>
       </c>
       <c r="D53">
-        <v>4637.421624064146</v>
+        <v>4574.235686307079</v>
       </c>
       <c r="E53">
-        <v>2174.724</v>
+        <v>2327.148</v>
       </c>
       <c r="F53">
-        <v>7773.624</v>
+        <v>7926.048</v>
       </c>
       <c r="G53">
         <v>1028.3</v>
@@ -5639,37 +5639,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M53">
-        <v>1560.9436992</v>
+        <v>1591.5504384</v>
       </c>
       <c r="N53">
-        <v>-1196.017168587755</v>
+        <v>-1226.623907787755</v>
       </c>
       <c r="O53">
-        <v>-239.2034337175511</v>
+        <v>-245.3247815575511</v>
       </c>
       <c r="P53">
-        <v>-956.8137348702043</v>
+        <v>-981.2991262302043</v>
       </c>
       <c r="Q53">
-        <v>139.5862651297958</v>
+        <v>115.1008737697958</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1232445975957809</v>
+        <v>0.1248580267123597</v>
       </c>
       <c r="T53">
-        <v>1.592342438420545</v>
+        <v>1.625516239220973</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.04675716757744349</v>
+        <v>0.04585799127787727</v>
       </c>
       <c r="W53">
-        <v>0.1914111607504493</v>
+        <v>0.1915917153514023</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2337858378872174</v>
+        <v>0.2292899563893863</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1595595448046618</v>
+        <v>0.1611095448046618</v>
       </c>
       <c r="C54">
-        <v>-2323.512313692921</v>
+        <v>-2537.423550727694</v>
       </c>
       <c r="D54">
-        <v>4574.235686307079</v>
+        <v>4512.748449272306</v>
       </c>
       <c r="E54">
-        <v>2327.148</v>
+        <v>2479.572000000001</v>
       </c>
       <c r="F54">
-        <v>7926.048</v>
+        <v>8078.472000000001</v>
       </c>
       <c r="G54">
         <v>1028.3</v>
@@ -5721,37 +5721,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M54">
-        <v>1591.5504384</v>
+        <v>1622.1571776</v>
       </c>
       <c r="N54">
-        <v>-1226.623907787755</v>
+        <v>-1257.230646987756</v>
       </c>
       <c r="O54">
-        <v>-245.3247815575511</v>
+        <v>-251.4461293975511</v>
       </c>
       <c r="P54">
-        <v>-981.2991262302043</v>
+        <v>-1005.784517590204</v>
       </c>
       <c r="Q54">
-        <v>115.1008737697958</v>
+        <v>90.61548240979562</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1248580267123597</v>
+        <v>0.1265401123870907</v>
       </c>
       <c r="T54">
-        <v>1.625516239220973</v>
+        <v>1.660101691119291</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.04585799127787727</v>
+        <v>0.04499274615942675</v>
       </c>
       <c r="W54">
-        <v>0.1915917153514023</v>
+        <v>0.1917654565711871</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2292899563893863</v>
+        <v>0.2249637307971337</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1611095448046618</v>
+        <v>0.1626595448046618</v>
       </c>
       <c r="C55">
-        <v>-2537.423550727694</v>
+        <v>-2749.703680648997</v>
       </c>
       <c r="D55">
-        <v>4512.748449272306</v>
+        <v>4452.892319351004</v>
       </c>
       <c r="E55">
-        <v>2479.572000000001</v>
+        <v>2631.996000000001</v>
       </c>
       <c r="F55">
-        <v>8078.472000000001</v>
+        <v>8230.896000000001</v>
       </c>
       <c r="G55">
         <v>1028.3</v>
@@ -5803,37 +5803,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M55">
-        <v>1622.1571776</v>
+        <v>1652.7639168</v>
       </c>
       <c r="N55">
-        <v>-1257.230646987756</v>
+        <v>-1287.837386187756</v>
       </c>
       <c r="O55">
-        <v>-251.4461293975511</v>
+        <v>-257.5674772375511</v>
       </c>
       <c r="P55">
-        <v>-1005.784517590204</v>
+        <v>-1030.269908950204</v>
       </c>
       <c r="Q55">
-        <v>90.61548240979562</v>
+        <v>66.13009104979574</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1265401123870907</v>
+        <v>0.1282953322215927</v>
       </c>
       <c r="T55">
-        <v>1.660101691119291</v>
+        <v>1.696190858317537</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.04499274615942675</v>
+        <v>0.0441595471564744</v>
       </c>
       <c r="W55">
-        <v>0.1917654565711871</v>
+        <v>0.1919327629309799</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2249637307971337</v>
+        <v>0.2207977357823721</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1626595448046618</v>
+        <v>0.1642095448046618</v>
       </c>
       <c r="C56">
-        <v>-2749.703680648997</v>
+        <v>-2960.416757820773</v>
       </c>
       <c r="D56">
-        <v>4452.892319351004</v>
+        <v>4394.603242179226</v>
       </c>
       <c r="E56">
-        <v>2631.996000000001</v>
+        <v>2784.42</v>
       </c>
       <c r="F56">
-        <v>8230.896000000001</v>
+        <v>8383.32</v>
       </c>
       <c r="G56">
         <v>1028.3</v>
@@ -5885,37 +5885,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M56">
-        <v>1652.7639168</v>
+        <v>1683.370656</v>
       </c>
       <c r="N56">
-        <v>-1287.837386187756</v>
+        <v>-1318.444125387755</v>
       </c>
       <c r="O56">
-        <v>-257.5674772375511</v>
+        <v>-263.6888250775511</v>
       </c>
       <c r="P56">
-        <v>-1030.269908950204</v>
+        <v>-1054.755300310204</v>
       </c>
       <c r="Q56">
-        <v>66.13009104979574</v>
+        <v>41.64469968979574</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1282953322215927</v>
+        <v>0.130128561826517</v>
       </c>
       <c r="T56">
-        <v>1.696190858317537</v>
+        <v>1.733883988502371</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.0441595471564744</v>
+        <v>0.04335664629908396</v>
       </c>
       <c r="W56">
-        <v>0.1919327629309799</v>
+        <v>0.1920939854231439</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2207977357823721</v>
+        <v>0.2167832314954198</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1642095448046618</v>
+        <v>0.1657595448046618</v>
       </c>
       <c r="C57">
-        <v>-2960.416757820773</v>
+        <v>-3169.623526015415</v>
       </c>
       <c r="D57">
-        <v>4394.603242179226</v>
+        <v>4337.820473984585</v>
       </c>
       <c r="E57">
-        <v>2784.42</v>
+        <v>2936.844000000001</v>
       </c>
       <c r="F57">
-        <v>8383.32</v>
+        <v>8535.744000000001</v>
       </c>
       <c r="G57">
         <v>1028.3</v>
@@ -5967,37 +5967,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M57">
-        <v>1683.370656</v>
+        <v>1713.9773952</v>
       </c>
       <c r="N57">
-        <v>-1318.444125387755</v>
+        <v>-1349.050864587756</v>
       </c>
       <c r="O57">
-        <v>-263.6888250775511</v>
+        <v>-269.8101729175511</v>
       </c>
       <c r="P57">
-        <v>-1054.755300310204</v>
+        <v>-1079.240691670204</v>
       </c>
       <c r="Q57">
-        <v>41.64469968979574</v>
+        <v>17.15930832979575</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.130128561826517</v>
+        <v>0.1320451200498469</v>
       </c>
       <c r="T57">
-        <v>1.733883988502371</v>
+        <v>1.773290442786516</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.04335664629908396</v>
+        <v>0.04258242047231461</v>
       </c>
       <c r="W57">
-        <v>0.1920939854231439</v>
+        <v>0.1922494499691592</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2167832314954198</v>
+        <v>0.212912102361573</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1657595448046618</v>
+        <v>0.1673095448046618</v>
       </c>
       <c r="C58">
-        <v>-3169.623526015415</v>
+        <v>-3377.381629566581</v>
       </c>
       <c r="D58">
-        <v>4337.820473984585</v>
+        <v>4282.48637043342</v>
       </c>
       <c r="E58">
-        <v>2936.844000000001</v>
+        <v>3089.268000000002</v>
       </c>
       <c r="F58">
-        <v>8535.744000000001</v>
+        <v>8688.168000000001</v>
       </c>
       <c r="G58">
         <v>1028.3</v>
@@ -6049,37 +6049,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M58">
-        <v>1713.9773952</v>
+        <v>1744.5841344</v>
       </c>
       <c r="N58">
-        <v>-1349.050864587756</v>
+        <v>-1379.657603787756</v>
       </c>
       <c r="O58">
-        <v>-269.8101729175511</v>
+        <v>-275.9315207575511</v>
       </c>
       <c r="P58">
-        <v>-1079.240691670204</v>
+        <v>-1103.726083030204</v>
       </c>
       <c r="Q58">
-        <v>17.15930832979575</v>
+        <v>-7.326083030204245</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1320451200498469</v>
+        <v>0.1340508205161224</v>
       </c>
       <c r="T58">
-        <v>1.773290442786516</v>
+        <v>1.814529755409458</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.04258242047231461</v>
+        <v>0.04183536046402839</v>
       </c>
       <c r="W58">
-        <v>0.1922494499691592</v>
+        <v>0.1923994596188231</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.212912102361573</v>
+        <v>0.2091768023201419</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1673095448046618</v>
+        <v>0.1688595448046618</v>
       </c>
       <c r="C59">
-        <v>-3377.381629566581</v>
+        <v>-3583.745808564548</v>
       </c>
       <c r="D59">
-        <v>4282.48637043342</v>
+        <v>4228.546191435453</v>
       </c>
       <c r="E59">
-        <v>3089.268000000002</v>
+        <v>3241.692000000001</v>
       </c>
       <c r="F59">
-        <v>8688.168000000001</v>
+        <v>8840.592000000001</v>
       </c>
       <c r="G59">
         <v>1028.3</v>
@@ -6131,37 +6131,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M59">
-        <v>1744.5841344</v>
+        <v>1775.1908736</v>
       </c>
       <c r="N59">
-        <v>-1379.657603787756</v>
+        <v>-1410.264342987756</v>
       </c>
       <c r="O59">
-        <v>-275.9315207575511</v>
+        <v>-282.0528685975511</v>
       </c>
       <c r="P59">
-        <v>-1103.726083030204</v>
+        <v>-1128.211474390204</v>
       </c>
       <c r="Q59">
-        <v>-7.326083030204245</v>
+        <v>-31.81147439020424</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1340508205161224</v>
+        <v>0.1361520305284111</v>
       </c>
       <c r="T59">
-        <v>1.814529755409458</v>
+        <v>1.857732844823969</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.04183536046402839</v>
+        <v>0.04111406114568306</v>
       </c>
       <c r="W59">
-        <v>0.1923994596188231</v>
+        <v>0.1925442965219469</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2091768023201419</v>
+        <v>0.2055703057284153</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1688595448046618</v>
+        <v>0.1704095448046618</v>
       </c>
       <c r="C60">
-        <v>-3583.745808564546</v>
+        <v>-3788.768079483515</v>
       </c>
       <c r="D60">
-        <v>4228.546191435453</v>
+        <v>4175.947920516484</v>
       </c>
       <c r="E60">
-        <v>3241.691999999999</v>
+        <v>3394.116</v>
       </c>
       <c r="F60">
-        <v>8840.591999999999</v>
+        <v>8993.016</v>
       </c>
       <c r="G60">
         <v>1028.3</v>
@@ -6213,37 +6213,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M60">
-        <v>1775.1908736</v>
+        <v>1805.7976128</v>
       </c>
       <c r="N60">
-        <v>-1410.264342987755</v>
+        <v>-1440.871082187755</v>
       </c>
       <c r="O60">
-        <v>-282.052868597551</v>
+        <v>-288.1742164375511</v>
       </c>
       <c r="P60">
-        <v>-1128.211474390204</v>
+        <v>-1152.696865750204</v>
       </c>
       <c r="Q60">
-        <v>-31.81147439020401</v>
+        <v>-56.29686575020423</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.136152030528411</v>
+        <v>0.1383557385900796</v>
       </c>
       <c r="T60">
-        <v>1.857732844823969</v>
+        <v>1.903043402014797</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.04111406114568308</v>
+        <v>0.04041721265168844</v>
       </c>
       <c r="W60">
-        <v>0.1925442965219469</v>
+        <v>0.192684223699541</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2055703057284154</v>
+        <v>0.2020860632584423</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1704095448046618</v>
+        <v>0.1930971426245822</v>
       </c>
       <c r="C61">
-        <v>-3788.768079483515</v>
+        <v>-4584.396864379317</v>
       </c>
       <c r="D61">
-        <v>4175.947920516484</v>
+        <v>3532.743135620682</v>
       </c>
       <c r="E61">
-        <v>3394.116</v>
+        <v>3546.539999999999</v>
       </c>
       <c r="F61">
-        <v>8993.016</v>
+        <v>9145.439999999999</v>
       </c>
       <c r="G61">
         <v>1028.3</v>
@@ -6295,45 +6295,45 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M61">
-        <v>1805.7976128</v>
+        <v>2156.494752</v>
       </c>
       <c r="N61">
-        <v>-1440.871082187755</v>
+        <v>-1791.568221387755</v>
       </c>
       <c r="O61">
-        <v>-288.1742164375511</v>
+        <v>-358.313644277551</v>
       </c>
       <c r="P61">
-        <v>-1152.696865750204</v>
+        <v>-1433.254577110204</v>
       </c>
       <c r="Q61">
-        <v>-56.29686575020423</v>
+        <v>-336.8545771102038</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1383557385900796</v>
+        <v>0.1410136266046325</v>
       </c>
       <c r="T61">
-        <v>1.903043402014797</v>
+        <v>1.95769237706961</v>
       </c>
       <c r="U61">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04041721265168844</v>
+        <v>0.0338444162939697</v>
       </c>
       <c r="W61">
-        <v>0.192684223699541</v>
+        <v>0.227819486637882</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.2020860632584423</v>
+        <v>0.1692220814698485</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1930971426245822</v>
+        <v>0.1949971426245822</v>
       </c>
       <c r="C62">
-        <v>-4584.396864379317</v>
+        <v>-4781.809741777385</v>
       </c>
       <c r="D62">
-        <v>3532.743135620682</v>
+        <v>3487.754258222615</v>
       </c>
       <c r="E62">
-        <v>3546.539999999999</v>
+        <v>3698.964</v>
       </c>
       <c r="F62">
-        <v>9145.439999999999</v>
+        <v>9297.864</v>
       </c>
       <c r="G62">
         <v>1028.3</v>
@@ -6377,37 +6377,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M62">
-        <v>2156.494752</v>
+        <v>2192.4363312</v>
       </c>
       <c r="N62">
-        <v>-1791.568221387755</v>
+        <v>-1827.509800587755</v>
       </c>
       <c r="O62">
-        <v>-358.313644277551</v>
+        <v>-365.5019601175511</v>
       </c>
       <c r="P62">
-        <v>-1433.254577110204</v>
+        <v>-1462.007840470204</v>
       </c>
       <c r="Q62">
-        <v>-336.8545771102038</v>
+        <v>-365.6078404702041</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1410136266046325</v>
+        <v>0.1434550016457769</v>
       </c>
       <c r="T62">
-        <v>1.95769237706961</v>
+        <v>2.007889617507293</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0338444162939697</v>
+        <v>0.03328958979734725</v>
       </c>
       <c r="W62">
-        <v>0.227819486637882</v>
+        <v>0.2279503147257855</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1692220814698485</v>
+        <v>0.1664479489867362</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1949971426245822</v>
+        <v>0.1968971426245821</v>
       </c>
       <c r="C63">
-        <v>-4781.809741777385</v>
+        <v>-4978.091176640252</v>
       </c>
       <c r="D63">
-        <v>3487.754258222615</v>
+        <v>3443.896823359748</v>
       </c>
       <c r="E63">
-        <v>3698.964</v>
+        <v>3851.388000000001</v>
       </c>
       <c r="F63">
-        <v>9297.864</v>
+        <v>9450.288</v>
       </c>
       <c r="G63">
         <v>1028.3</v>
@@ -6459,37 +6459,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M63">
-        <v>2192.4363312</v>
+        <v>2228.3779104</v>
       </c>
       <c r="N63">
-        <v>-1827.509800587755</v>
+        <v>-1863.451379787755</v>
       </c>
       <c r="O63">
-        <v>-365.5019601175511</v>
+        <v>-372.6902759575511</v>
       </c>
       <c r="P63">
-        <v>-1462.007840470204</v>
+        <v>-1490.761103830204</v>
       </c>
       <c r="Q63">
-        <v>-365.6078404702041</v>
+        <v>-394.3611038302042</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1434550016457769</v>
+        <v>0.1460248701101395</v>
       </c>
       <c r="T63">
-        <v>2.007889617507293</v>
+        <v>2.060728817968011</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03328958979734725</v>
+        <v>0.0327526609296481</v>
       </c>
       <c r="W63">
-        <v>0.2279503147257855</v>
+        <v>0.228076922552789</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1664479489867362</v>
+        <v>0.1637633046482405</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1968971426245821</v>
+        <v>0.1987971426245822</v>
       </c>
       <c r="C64">
-        <v>-4978.091176640252</v>
+        <v>-5173.283321535869</v>
       </c>
       <c r="D64">
-        <v>3443.896823359748</v>
+        <v>3401.128678464131</v>
       </c>
       <c r="E64">
-        <v>3851.388000000001</v>
+        <v>4003.812</v>
       </c>
       <c r="F64">
-        <v>9450.288</v>
+        <v>9602.712</v>
       </c>
       <c r="G64">
         <v>1028.3</v>
@@ -6541,37 +6541,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M64">
-        <v>2228.3779104</v>
+        <v>2264.3194896</v>
       </c>
       <c r="N64">
-        <v>-1863.451379787755</v>
+        <v>-1899.392958987755</v>
       </c>
       <c r="O64">
-        <v>-372.6902759575511</v>
+        <v>-379.8785917975511</v>
       </c>
       <c r="P64">
-        <v>-1490.761103830204</v>
+        <v>-1519.514367190204</v>
       </c>
       <c r="Q64">
-        <v>-394.3611038302042</v>
+        <v>-423.1143671902041</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1460248701101395</v>
+        <v>0.1487336503833865</v>
       </c>
       <c r="T64">
-        <v>2.060728817968011</v>
+        <v>2.116424191426606</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0327526609296481</v>
+        <v>0.03223277742282828</v>
       </c>
       <c r="W64">
-        <v>0.228076922552789</v>
+        <v>0.2281995110836971</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1637633046482405</v>
+        <v>0.1611638871141414</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1987971426245822</v>
+        <v>0.2006971426245822</v>
       </c>
       <c r="C65">
-        <v>-5173.283321535869</v>
+        <v>-5367.426260824143</v>
       </c>
       <c r="D65">
-        <v>3401.128678464131</v>
+        <v>3359.409739175857</v>
       </c>
       <c r="E65">
-        <v>4003.812</v>
+        <v>4156.236000000001</v>
       </c>
       <c r="F65">
-        <v>9602.712</v>
+        <v>9755.136</v>
       </c>
       <c r="G65">
         <v>1028.3</v>
@@ -6623,37 +6623,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M65">
-        <v>2264.3194896</v>
+        <v>2300.2610688</v>
       </c>
       <c r="N65">
-        <v>-1899.392958987755</v>
+        <v>-1935.334538187755</v>
       </c>
       <c r="O65">
-        <v>-379.8785917975511</v>
+        <v>-387.0669076375511</v>
       </c>
       <c r="P65">
-        <v>-1519.514367190204</v>
+        <v>-1548.267630550204</v>
       </c>
       <c r="Q65">
-        <v>-423.1143671902041</v>
+        <v>-451.867630550204</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1487336503833865</v>
+        <v>0.1515929184495917</v>
       </c>
       <c r="T65">
-        <v>2.116424191426606</v>
+        <v>2.175213752299567</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03223277742282828</v>
+        <v>0.0317291402755966</v>
       </c>
       <c r="W65">
-        <v>0.2281995110836971</v>
+        <v>0.2283182687230143</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1611638871141414</v>
+        <v>0.158645701377983</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2006971426245822</v>
+        <v>0.2025971426245822</v>
       </c>
       <c r="C66">
-        <v>-5367.426260824143</v>
+        <v>-5560.558135965187</v>
       </c>
       <c r="D66">
-        <v>3359.409739175857</v>
+        <v>3318.701864034812</v>
       </c>
       <c r="E66">
-        <v>4156.236000000001</v>
+        <v>4308.66</v>
       </c>
       <c r="F66">
-        <v>9755.136</v>
+        <v>9907.559999999999</v>
       </c>
       <c r="G66">
         <v>1028.3</v>
@@ -6705,37 +6705,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M66">
-        <v>2300.2610688</v>
+        <v>2336.202648</v>
       </c>
       <c r="N66">
-        <v>-1935.334538187755</v>
+        <v>-1971.276117387755</v>
       </c>
       <c r="O66">
-        <v>-387.0669076375511</v>
+        <v>-394.2552234775511</v>
       </c>
       <c r="P66">
-        <v>-1548.267630550204</v>
+        <v>-1577.020893910204</v>
       </c>
       <c r="Q66">
-        <v>-451.867630550204</v>
+        <v>-480.6208939102041</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1515929184495917</v>
+        <v>0.1546155732624371</v>
       </c>
       <c r="T66">
-        <v>2.175213752299567</v>
+        <v>2.237362716650984</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0317291402755966</v>
+        <v>0.03124099965597203</v>
       </c>
       <c r="W66">
-        <v>0.2283182687230143</v>
+        <v>0.2284333722811218</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.158645701377983</v>
+        <v>0.1562049982798601</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2025971426245822</v>
+        <v>0.2044971426245822</v>
       </c>
       <c r="C67">
-        <v>-5560.558135965187</v>
+        <v>-5752.715261826078</v>
       </c>
       <c r="D67">
-        <v>3318.701864034812</v>
+        <v>3278.968738173923</v>
       </c>
       <c r="E67">
-        <v>4308.66</v>
+        <v>4461.084000000001</v>
       </c>
       <c r="F67">
-        <v>9907.559999999999</v>
+        <v>10059.984</v>
       </c>
       <c r="G67">
         <v>1028.3</v>
@@ -6787,37 +6787,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M67">
-        <v>2336.202648</v>
+        <v>2372.1442272</v>
       </c>
       <c r="N67">
-        <v>-1971.276117387755</v>
+        <v>-2007.217696587756</v>
       </c>
       <c r="O67">
-        <v>-394.2552234775511</v>
+        <v>-401.4435393175511</v>
       </c>
       <c r="P67">
-        <v>-1577.020893910204</v>
+        <v>-1605.774157270205</v>
       </c>
       <c r="Q67">
-        <v>-480.6208939102041</v>
+        <v>-509.3741572702045</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1546155732624371</v>
+        <v>0.1578160312995676</v>
       </c>
       <c r="T67">
-        <v>2.237362716650984</v>
+        <v>2.303167502434836</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03124099965597203</v>
+        <v>0.03076765117633609</v>
       </c>
       <c r="W67">
-        <v>0.2284333722811218</v>
+        <v>0.22854498785262</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1562049982798601</v>
+        <v>0.1538382558816804</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2044971426245822</v>
+        <v>0.2063971426245822</v>
       </c>
       <c r="C68">
-        <v>-5752.715261826078</v>
+        <v>-5943.932234731544</v>
       </c>
       <c r="D68">
-        <v>3278.968738173923</v>
+        <v>3240.175765268458</v>
       </c>
       <c r="E68">
-        <v>4461.084000000001</v>
+        <v>4613.508000000002</v>
       </c>
       <c r="F68">
-        <v>10059.984</v>
+        <v>10212.408</v>
       </c>
       <c r="G68">
         <v>1028.3</v>
@@ -6869,37 +6869,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M68">
-        <v>2372.1442272</v>
+        <v>2408.0858064</v>
       </c>
       <c r="N68">
-        <v>-2007.217696587756</v>
+        <v>-2043.159275787756</v>
       </c>
       <c r="O68">
-        <v>-401.4435393175511</v>
+        <v>-408.6318551575512</v>
       </c>
       <c r="P68">
-        <v>-1605.774157270205</v>
+        <v>-1634.527420630204</v>
       </c>
       <c r="Q68">
-        <v>-509.3741572702045</v>
+        <v>-538.1274206302044</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1578160312995676</v>
+        <v>0.1612104564904636</v>
       </c>
       <c r="T68">
-        <v>2.303167502434836</v>
+        <v>2.372960457054074</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03076765117633609</v>
+        <v>0.03030843250206242</v>
       </c>
       <c r="W68">
-        <v>0.22854498785262</v>
+        <v>0.2286532716160137</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1538382558816804</v>
+        <v>0.1515421625103121</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2063971426245822</v>
+        <v>0.2082971426245822</v>
       </c>
       <c r="C69">
-        <v>-5943.932234731544</v>
+        <v>-6134.242032934364</v>
       </c>
       <c r="D69">
-        <v>3240.175765268458</v>
+        <v>3202.289967065637</v>
       </c>
       <c r="E69">
-        <v>4613.508000000002</v>
+        <v>4765.932000000001</v>
       </c>
       <c r="F69">
-        <v>10212.408</v>
+        <v>10364.832</v>
       </c>
       <c r="G69">
         <v>1028.3</v>
@@ -6951,37 +6951,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M69">
-        <v>2408.0858064</v>
+        <v>2444.0273856</v>
       </c>
       <c r="N69">
-        <v>-2043.159275787756</v>
+        <v>-2079.100854987756</v>
       </c>
       <c r="O69">
-        <v>-408.6318551575512</v>
+        <v>-415.8201709975511</v>
       </c>
       <c r="P69">
-        <v>-1634.527420630204</v>
+        <v>-1663.280683990205</v>
       </c>
       <c r="Q69">
-        <v>-538.1274206302044</v>
+        <v>-566.8806839902045</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1612104564904636</v>
+        <v>0.1648170332557906</v>
       </c>
       <c r="T69">
-        <v>2.372960457054074</v>
+        <v>2.447115471337014</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03030843250206242</v>
+        <v>0.02986272025938502</v>
       </c>
       <c r="W69">
-        <v>0.2286532716160137</v>
+        <v>0.228758370562837</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1515421625103121</v>
+        <v>0.1493136012969252</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2082971426245822</v>
+        <v>0.2101971426245822</v>
       </c>
       <c r="C70">
-        <v>-6134.242032934364</v>
+        <v>-6323.67611011873</v>
       </c>
       <c r="D70">
-        <v>3202.289967065637</v>
+        <v>3165.279889881271</v>
       </c>
       <c r="E70">
-        <v>4765.932000000001</v>
+        <v>4918.356000000002</v>
       </c>
       <c r="F70">
-        <v>10364.832</v>
+        <v>10517.256</v>
       </c>
       <c r="G70">
         <v>1028.3</v>
@@ -7033,37 +7033,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M70">
-        <v>2444.0273856</v>
+        <v>2479.9689648</v>
       </c>
       <c r="N70">
-        <v>-2079.100854987756</v>
+        <v>-2115.042434187756</v>
       </c>
       <c r="O70">
-        <v>-415.8201709975511</v>
+        <v>-423.0084868375511</v>
       </c>
       <c r="P70">
-        <v>-1663.280683990205</v>
+        <v>-1692.033947350204</v>
       </c>
       <c r="Q70">
-        <v>-566.8806839902045</v>
+        <v>-595.6339473502044</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1648170332557906</v>
+        <v>0.1686562923930742</v>
       </c>
       <c r="T70">
-        <v>2.447115471337014</v>
+        <v>2.526054680089821</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02986272025938502</v>
+        <v>0.02942992721214756</v>
       </c>
       <c r="W70">
-        <v>0.228758370562837</v>
+        <v>0.2288604231633756</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1493136012969252</v>
+        <v>0.1471496360607378</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2101971426245822</v>
+        <v>0.2120971426245822</v>
       </c>
       <c r="C71">
-        <v>-6323.67611011873</v>
+        <v>-6512.264482493731</v>
       </c>
       <c r="D71">
-        <v>3165.279889881271</v>
+        <v>3129.115517506269</v>
       </c>
       <c r="E71">
-        <v>4918.356000000002</v>
+        <v>5070.780000000001</v>
       </c>
       <c r="F71">
-        <v>10517.256</v>
+        <v>10669.68</v>
       </c>
       <c r="G71">
         <v>1028.3</v>
@@ -7115,37 +7115,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M71">
-        <v>2479.9689648</v>
+        <v>2515.910544</v>
       </c>
       <c r="N71">
-        <v>-2115.042434187756</v>
+        <v>-2150.984013387756</v>
       </c>
       <c r="O71">
-        <v>-423.0084868375511</v>
+        <v>-430.1968026775511</v>
       </c>
       <c r="P71">
-        <v>-1692.033947350204</v>
+        <v>-1720.787210710204</v>
       </c>
       <c r="Q71">
-        <v>-595.6339473502044</v>
+        <v>-624.3872107102043</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1686562923930742</v>
+        <v>0.17275150213951</v>
       </c>
       <c r="T71">
-        <v>2.526054680089821</v>
+        <v>2.610256502759481</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02942992721214756</v>
+        <v>0.02900949968054545</v>
       </c>
       <c r="W71">
-        <v>0.2288604231633756</v>
+        <v>0.2289595599753274</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1471496360607378</v>
+        <v>0.1450474984027272</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2120971426245822</v>
+        <v>0.2139971426245822</v>
       </c>
       <c r="C72">
-        <v>-6512.264482493731</v>
+        <v>-6700.035809983903</v>
       </c>
       <c r="D72">
-        <v>3129.115517506269</v>
+        <v>3093.768190016098</v>
       </c>
       <c r="E72">
-        <v>5070.780000000001</v>
+        <v>5223.204000000002</v>
       </c>
       <c r="F72">
-        <v>10669.68</v>
+        <v>10822.104</v>
       </c>
       <c r="G72">
         <v>1028.3</v>
@@ -7197,37 +7197,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M72">
-        <v>2515.910544</v>
+        <v>2551.8521232</v>
       </c>
       <c r="N72">
-        <v>-2150.984013387756</v>
+        <v>-2186.925592587756</v>
       </c>
       <c r="O72">
-        <v>-430.1968026775511</v>
+        <v>-437.3851185175511</v>
       </c>
       <c r="P72">
-        <v>-1720.787210710204</v>
+        <v>-1749.540474070204</v>
       </c>
       <c r="Q72">
-        <v>-624.3872107102043</v>
+        <v>-653.1404740702044</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.17275150213951</v>
+        <v>0.1771291401443207</v>
       </c>
       <c r="T72">
-        <v>2.610256502759481</v>
+        <v>2.700265347682222</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02900949968054545</v>
+        <v>0.02860091517800256</v>
       </c>
       <c r="W72">
-        <v>0.2289595599753274</v>
+        <v>0.229055904201027</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1450474984027272</v>
+        <v>0.1430045758900128</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2139971426245822</v>
+        <v>0.2158971426245822</v>
       </c>
       <c r="C73">
-        <v>-6700.0358099839</v>
+        <v>-6887.017471978283</v>
       </c>
       <c r="D73">
-        <v>3093.768190016099</v>
+        <v>3059.210528021716</v>
       </c>
       <c r="E73">
-        <v>5223.204</v>
+        <v>5375.627999999999</v>
       </c>
       <c r="F73">
-        <v>10822.104</v>
+        <v>10974.528</v>
       </c>
       <c r="G73">
         <v>1028.3</v>
@@ -7279,37 +7279,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M73">
-        <v>2551.8521232</v>
+        <v>2587.7937024</v>
       </c>
       <c r="N73">
-        <v>-2186.925592587755</v>
+        <v>-2222.867171787755</v>
       </c>
       <c r="O73">
-        <v>-437.3851185175511</v>
+        <v>-444.573434357551</v>
       </c>
       <c r="P73">
-        <v>-1749.540474070204</v>
+        <v>-1778.293737430204</v>
       </c>
       <c r="Q73">
-        <v>-653.1404740702039</v>
+        <v>-681.8937374302041</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1771291401443207</v>
+        <v>0.1818194665780464</v>
       </c>
       <c r="T73">
-        <v>2.700265347682221</v>
+        <v>2.796703395813729</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02860091517800257</v>
+        <v>0.02820368024497475</v>
       </c>
       <c r="W73">
-        <v>0.229055904201027</v>
+        <v>0.229149572198235</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1430045758900128</v>
+        <v>0.1410184012248737</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2158971426245822</v>
+        <v>0.2177971426245822</v>
       </c>
       <c r="C74">
-        <v>-6887.017471978283</v>
+        <v>-7073.235638058868</v>
       </c>
       <c r="D74">
-        <v>3059.210528021716</v>
+        <v>3025.416361941131</v>
       </c>
       <c r="E74">
-        <v>5375.627999999999</v>
+        <v>5528.052</v>
       </c>
       <c r="F74">
-        <v>10974.528</v>
+        <v>11126.952</v>
       </c>
       <c r="G74">
         <v>1028.3</v>
@@ -7361,37 +7361,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M74">
-        <v>2587.7937024</v>
+        <v>2623.7352816</v>
       </c>
       <c r="N74">
-        <v>-2222.867171787755</v>
+        <v>-2258.808750987755</v>
       </c>
       <c r="O74">
-        <v>-444.573434357551</v>
+        <v>-451.761750197551</v>
       </c>
       <c r="P74">
-        <v>-1778.293737430204</v>
+        <v>-1807.047000790204</v>
       </c>
       <c r="Q74">
-        <v>-681.8937374302041</v>
+        <v>-710.6470007902039</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1818194665780464</v>
+        <v>0.1868572245994555</v>
       </c>
       <c r="T74">
-        <v>2.796703395813729</v>
+        <v>2.900285003066089</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02820368024497475</v>
+        <v>0.02781732846079701</v>
       </c>
       <c r="W74">
-        <v>0.229149572198235</v>
+        <v>0.2292406739489441</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1410184012248737</v>
+        <v>0.139086642303985</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2177971426245822</v>
+        <v>0.2196971426245822</v>
       </c>
       <c r="C75">
-        <v>-7073.235638058868</v>
+        <v>-7258.715334092345</v>
       </c>
       <c r="D75">
-        <v>3025.416361941131</v>
+        <v>2992.360665907655</v>
       </c>
       <c r="E75">
-        <v>5528.052</v>
+        <v>5680.476000000001</v>
       </c>
       <c r="F75">
-        <v>11126.952</v>
+        <v>11279.376</v>
       </c>
       <c r="G75">
         <v>1028.3</v>
@@ -7443,37 +7443,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M75">
-        <v>2623.7352816</v>
+        <v>2659.6768608</v>
       </c>
       <c r="N75">
-        <v>-2258.808750987755</v>
+        <v>-2294.750330187755</v>
       </c>
       <c r="O75">
-        <v>-451.761750197551</v>
+        <v>-458.9500660375511</v>
       </c>
       <c r="P75">
-        <v>-1807.047000790204</v>
+        <v>-1835.800264150204</v>
       </c>
       <c r="Q75">
-        <v>-710.6470007902039</v>
+        <v>-739.4002641502043</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1868572245994555</v>
+        <v>0.1922825024686654</v>
       </c>
       <c r="T75">
-        <v>2.900285003066089</v>
+        <v>3.011834426260939</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02781732846079701</v>
+        <v>0.02744141861673219</v>
       </c>
       <c r="W75">
-        <v>0.2292406739489441</v>
+        <v>0.2293293134901745</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.139086642303985</v>
+        <v>0.137207093083661</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2196971426245822</v>
+        <v>0.2215971426245822</v>
       </c>
       <c r="C76">
-        <v>-7258.715334092345</v>
+        <v>-7443.480504035964</v>
       </c>
       <c r="D76">
-        <v>2992.360665907655</v>
+        <v>2960.019495964035</v>
       </c>
       <c r="E76">
-        <v>5680.476000000001</v>
+        <v>5832.9</v>
       </c>
       <c r="F76">
-        <v>11279.376</v>
+        <v>11431.8</v>
       </c>
       <c r="G76">
         <v>1028.3</v>
@@ -7525,37 +7525,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M76">
-        <v>2659.6768608</v>
+        <v>2695.61844</v>
       </c>
       <c r="N76">
-        <v>-2294.750330187755</v>
+        <v>-2330.691909387755</v>
       </c>
       <c r="O76">
-        <v>-458.9500660375511</v>
+        <v>-466.138381877551</v>
       </c>
       <c r="P76">
-        <v>-1835.800264150204</v>
+        <v>-1864.553527510204</v>
       </c>
       <c r="Q76">
-        <v>-739.4002641502043</v>
+        <v>-768.153527510204</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1922825024686654</v>
+        <v>0.198141802567412</v>
       </c>
       <c r="T76">
-        <v>3.011834426260939</v>
+        <v>3.132307803311377</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02744141861673219</v>
+        <v>0.02707553303517576</v>
       </c>
       <c r="W76">
-        <v>0.2293293134901745</v>
+        <v>0.2294155893103056</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.137207093083661</v>
+        <v>0.1353776651758788</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2215971426245822</v>
+        <v>0.2234971426245822</v>
       </c>
       <c r="C77">
-        <v>-7443.480504035964</v>
+        <v>-7627.554067778325</v>
       </c>
       <c r="D77">
-        <v>2960.019495964035</v>
+        <v>2928.369932221675</v>
       </c>
       <c r="E77">
-        <v>5832.9</v>
+        <v>5985.324000000001</v>
       </c>
       <c r="F77">
-        <v>11431.8</v>
+        <v>11584.224</v>
       </c>
       <c r="G77">
         <v>1028.3</v>
@@ -7607,37 +7607,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M77">
-        <v>2695.61844</v>
+        <v>2731.5600192</v>
       </c>
       <c r="N77">
-        <v>-2330.691909387755</v>
+        <v>-2366.633488587755</v>
       </c>
       <c r="O77">
-        <v>-466.138381877551</v>
+        <v>-473.3266977175511</v>
       </c>
       <c r="P77">
-        <v>-1864.553527510204</v>
+        <v>-1893.306790870204</v>
       </c>
       <c r="Q77">
-        <v>-768.153527510204</v>
+        <v>-796.9067908702043</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.198141802567412</v>
+        <v>0.2044893776743875</v>
       </c>
       <c r="T77">
-        <v>3.132307803311377</v>
+        <v>3.262820628449351</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02707553303517576</v>
+        <v>0.02671927602155502</v>
       </c>
       <c r="W77">
-        <v>0.2294155893103056</v>
+        <v>0.2294995947141173</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1353776651758788</v>
+        <v>0.1335963801077751</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2234971426245822</v>
+        <v>0.2253971426245822</v>
       </c>
       <c r="C78">
-        <v>-7627.554067778325</v>
+        <v>-7810.957975308654</v>
       </c>
       <c r="D78">
-        <v>2928.369932221675</v>
+        <v>2897.390024691346</v>
       </c>
       <c r="E78">
-        <v>5985.324000000001</v>
+        <v>6137.748</v>
       </c>
       <c r="F78">
-        <v>11584.224</v>
+        <v>11736.648</v>
       </c>
       <c r="G78">
         <v>1028.3</v>
@@ -7689,37 +7689,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M78">
-        <v>2731.5600192</v>
+        <v>2767.5015984</v>
       </c>
       <c r="N78">
-        <v>-2366.633488587755</v>
+        <v>-2402.575067787755</v>
       </c>
       <c r="O78">
-        <v>-473.3266977175511</v>
+        <v>-480.5150135575511</v>
       </c>
       <c r="P78">
-        <v>-1893.306790870204</v>
+        <v>-1922.060054230204</v>
       </c>
       <c r="Q78">
-        <v>-796.9067908702043</v>
+        <v>-825.6600542302042</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2044893776743875</v>
+        <v>0.2113889158341435</v>
       </c>
       <c r="T78">
-        <v>3.262820628449351</v>
+        <v>3.40468239490367</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02671927602155502</v>
+        <v>0.02637227243685951</v>
       </c>
       <c r="W78">
-        <v>0.2294995947141173</v>
+        <v>0.2295814181593885</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1335963801077751</v>
+        <v>0.1318613621842976</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2253971426245822</v>
+        <v>0.2272971426245822</v>
       </c>
       <c r="C79">
-        <v>-7810.957975308654</v>
+        <v>-7993.713257483716</v>
       </c>
       <c r="D79">
-        <v>2897.390024691346</v>
+        <v>2867.058742516284</v>
       </c>
       <c r="E79">
-        <v>6137.748</v>
+        <v>6290.172</v>
       </c>
       <c r="F79">
-        <v>11736.648</v>
+        <v>11889.072</v>
       </c>
       <c r="G79">
         <v>1028.3</v>
@@ -7771,37 +7771,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M79">
-        <v>2767.5015984</v>
+        <v>2803.4431776</v>
       </c>
       <c r="N79">
-        <v>-2402.575067787755</v>
+        <v>-2438.516646987755</v>
       </c>
       <c r="O79">
-        <v>-480.5150135575511</v>
+        <v>-487.7033293975511</v>
       </c>
       <c r="P79">
-        <v>-1922.060054230204</v>
+        <v>-1950.813317590204</v>
       </c>
       <c r="Q79">
-        <v>-825.6600542302042</v>
+        <v>-854.4133175902043</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2113889158341435</v>
+        <v>0.2189156847356954</v>
       </c>
       <c r="T79">
-        <v>3.40468239490367</v>
+        <v>3.55944068558111</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02637227243685951</v>
+        <v>0.02603416637997669</v>
       </c>
       <c r="W79">
-        <v>0.2295814181593885</v>
+        <v>0.2296611435676015</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1318613621842976</v>
+        <v>0.1301708318998834</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2272971426245822</v>
+        <v>0.2291971426245822</v>
       </c>
       <c r="C80">
-        <v>-7993.713257483716</v>
+        <v>-8175.840073638994</v>
       </c>
       <c r="D80">
-        <v>2867.058742516284</v>
+        <v>2837.355926361007</v>
       </c>
       <c r="E80">
-        <v>6290.172</v>
+        <v>6442.596000000001</v>
       </c>
       <c r="F80">
-        <v>11889.072</v>
+        <v>12041.496</v>
       </c>
       <c r="G80">
         <v>1028.3</v>
@@ -7853,37 +7853,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M80">
-        <v>2803.4431776</v>
+        <v>2839.384756800001</v>
       </c>
       <c r="N80">
-        <v>-2438.516646987755</v>
+        <v>-2474.458226187756</v>
       </c>
       <c r="O80">
-        <v>-487.7033293975511</v>
+        <v>-494.8916452375512</v>
       </c>
       <c r="P80">
-        <v>-1950.813317590204</v>
+        <v>-1979.566580950205</v>
       </c>
       <c r="Q80">
-        <v>-854.4133175902043</v>
+        <v>-883.1665809502047</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2189156847356954</v>
+        <v>0.2271592887707286</v>
       </c>
       <c r="T80">
-        <v>3.55944068558111</v>
+        <v>3.728937861084973</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02603416637997669</v>
+        <v>0.02570461997010356</v>
       </c>
       <c r="W80">
-        <v>0.2296611435676015</v>
+        <v>0.2297388506110496</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1301708318998834</v>
+        <v>0.1285230998505178</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2291971426245822</v>
+        <v>0.2310971426245822</v>
       </c>
       <c r="C81">
-        <v>-8175.840073638994</v>
+        <v>-8357.357756270721</v>
       </c>
       <c r="D81">
-        <v>2837.355926361007</v>
+        <v>2808.262243729278</v>
       </c>
       <c r="E81">
-        <v>6442.596000000001</v>
+        <v>6595.02</v>
       </c>
       <c r="F81">
-        <v>12041.496</v>
+        <v>12193.92</v>
       </c>
       <c r="G81">
         <v>1028.3</v>
@@ -7935,37 +7935,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M81">
-        <v>2839.384756800001</v>
+        <v>2875.326336</v>
       </c>
       <c r="N81">
-        <v>-2474.458226187756</v>
+        <v>-2510.399805387755</v>
       </c>
       <c r="O81">
-        <v>-494.8916452375512</v>
+        <v>-502.0799610775511</v>
       </c>
       <c r="P81">
-        <v>-1979.566580950205</v>
+        <v>-2008.319844310204</v>
       </c>
       <c r="Q81">
-        <v>-883.1665809502047</v>
+        <v>-911.9198443102041</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2271592887707286</v>
+        <v>0.236227253209265</v>
       </c>
       <c r="T81">
-        <v>3.728937861084973</v>
+        <v>3.915384754139221</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02570461997010356</v>
+        <v>0.02538331222047727</v>
       </c>
       <c r="W81">
-        <v>0.2297388506110496</v>
+        <v>0.2298146149784115</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1285230998505178</v>
+        <v>0.1269165611023864</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2310971426245822</v>
+        <v>0.2329971426245822</v>
       </c>
       <c r="C82">
-        <v>-8357.357756270721</v>
+        <v>-8538.284852996863</v>
       </c>
       <c r="D82">
-        <v>2808.262243729278</v>
+        <v>2779.759147003138</v>
       </c>
       <c r="E82">
-        <v>6595.02</v>
+        <v>6747.444000000001</v>
       </c>
       <c r="F82">
-        <v>12193.92</v>
+        <v>12346.344</v>
       </c>
       <c r="G82">
         <v>1028.3</v>
@@ -8017,37 +8017,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M82">
-        <v>2875.326336</v>
+        <v>2911.267915200001</v>
       </c>
       <c r="N82">
-        <v>-2510.399805387755</v>
+        <v>-2546.341384587756</v>
       </c>
       <c r="O82">
-        <v>-502.0799610775511</v>
+        <v>-509.2682769175512</v>
       </c>
       <c r="P82">
-        <v>-2008.319844310204</v>
+        <v>-2037.073107670205</v>
       </c>
       <c r="Q82">
-        <v>-911.9198443102041</v>
+        <v>-940.6731076702044</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.236227253209265</v>
+        <v>0.2462497402202789</v>
       </c>
       <c r="T82">
-        <v>3.915384754139221</v>
+        <v>4.121457635936022</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02538331222047727</v>
+        <v>0.0250699379955331</v>
       </c>
       <c r="W82">
-        <v>0.2298146149784115</v>
+        <v>0.2298885086206533</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1269165611023864</v>
+        <v>0.1253496899776655</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2329971426245822</v>
+        <v>0.2348971426245822</v>
       </c>
       <c r="C83">
-        <v>-8538.284852996863</v>
+        <v>-8718.639165988377</v>
       </c>
       <c r="D83">
-        <v>2779.759147003138</v>
+        <v>2751.828834011622</v>
       </c>
       <c r="E83">
-        <v>6747.444000000001</v>
+        <v>6899.868</v>
       </c>
       <c r="F83">
-        <v>12346.344</v>
+        <v>12498.768</v>
       </c>
       <c r="G83">
         <v>1028.3</v>
@@ -8099,37 +8099,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M83">
-        <v>2911.267915200001</v>
+        <v>2947.2094944</v>
       </c>
       <c r="N83">
-        <v>-2546.341384587756</v>
+        <v>-2582.282963787755</v>
       </c>
       <c r="O83">
-        <v>-509.2682769175512</v>
+        <v>-516.4565927575511</v>
       </c>
       <c r="P83">
-        <v>-2037.073107670205</v>
+        <v>-2065.826371030204</v>
       </c>
       <c r="Q83">
-        <v>-940.6731076702044</v>
+        <v>-969.4263710302043</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2462497402202789</v>
+        <v>0.2573858368991833</v>
       </c>
       <c r="T83">
-        <v>4.121457635936022</v>
+        <v>4.350427504599136</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0250699379955331</v>
+        <v>0.02476420704436808</v>
       </c>
       <c r="W83">
-        <v>0.2298885086206533</v>
+        <v>0.229960599978938</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1253496899776655</v>
+        <v>0.1238210352218404</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2348971426245822</v>
+        <v>0.2367971426245822</v>
       </c>
       <c r="C84">
-        <v>-8718.639165988377</v>
+        <v>-8898.437789047004</v>
       </c>
       <c r="D84">
-        <v>2751.828834011622</v>
+        <v>2724.454210952997</v>
       </c>
       <c r="E84">
-        <v>6899.868</v>
+        <v>7052.292000000001</v>
       </c>
       <c r="F84">
-        <v>12498.768</v>
+        <v>12651.192</v>
       </c>
       <c r="G84">
         <v>1028.3</v>
@@ -8181,37 +8181,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M84">
-        <v>2947.2094944</v>
+        <v>2983.1510736</v>
       </c>
       <c r="N84">
-        <v>-2582.282963787755</v>
+        <v>-2618.224542987756</v>
       </c>
       <c r="O84">
-        <v>-516.4565927575511</v>
+        <v>-523.6449085975512</v>
       </c>
       <c r="P84">
-        <v>-2065.826371030204</v>
+        <v>-2094.579634390205</v>
       </c>
       <c r="Q84">
-        <v>-969.4263710302043</v>
+        <v>-998.1796343902047</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2573858368991833</v>
+        <v>0.2698320625991353</v>
       </c>
       <c r="T84">
-        <v>4.350427504599136</v>
+        <v>4.606335004869673</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02476420704436808</v>
+        <v>0.02446584310407448</v>
       </c>
       <c r="W84">
-        <v>0.229960599978938</v>
+        <v>0.2300309541960592</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1238210352218404</v>
+        <v>0.1223292155203723</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2367971426245822</v>
+        <v>0.2386971426245822</v>
       </c>
       <c r="C85">
-        <v>-8898.437789047004</v>
+        <v>-9077.697142491743</v>
       </c>
       <c r="D85">
-        <v>2724.454210952997</v>
+        <v>2697.618857508259</v>
       </c>
       <c r="E85">
-        <v>7052.292000000001</v>
+        <v>7204.716000000002</v>
       </c>
       <c r="F85">
-        <v>12651.192</v>
+        <v>12803.616</v>
       </c>
       <c r="G85">
         <v>1028.3</v>
@@ -8263,37 +8263,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M85">
-        <v>2983.1510736</v>
+        <v>3019.0926528</v>
       </c>
       <c r="N85">
-        <v>-2618.224542987756</v>
+        <v>-2654.166122187756</v>
       </c>
       <c r="O85">
-        <v>-523.6449085975512</v>
+        <v>-530.8332244375512</v>
       </c>
       <c r="P85">
-        <v>-2094.579634390205</v>
+        <v>-2123.332897750205</v>
       </c>
       <c r="Q85">
-        <v>-998.1796343902047</v>
+        <v>-1026.932897750205</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2698320625991353</v>
+        <v>0.2838340665115813</v>
       </c>
       <c r="T85">
-        <v>4.606335004869673</v>
+        <v>4.894230942674029</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02446584310407448</v>
+        <v>0.02417458306712121</v>
       </c>
       <c r="W85">
-        <v>0.2300309541960592</v>
+        <v>0.2300996333127728</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1223292155203723</v>
+        <v>0.1208729153356061</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2386971426245822</v>
+        <v>0.2405971426245822</v>
       </c>
       <c r="C86">
-        <v>-9077.697142491741</v>
+        <v>-9256.433006003741</v>
       </c>
       <c r="D86">
-        <v>2697.618857508259</v>
+        <v>2671.306993996258</v>
       </c>
       <c r="E86">
-        <v>7204.716</v>
+        <v>7357.139999999999</v>
       </c>
       <c r="F86">
-        <v>12803.616</v>
+        <v>12956.04</v>
       </c>
       <c r="G86">
         <v>1028.3</v>
@@ -8345,37 +8345,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M86">
-        <v>3019.0926528</v>
+        <v>3055.034232</v>
       </c>
       <c r="N86">
-        <v>-2654.166122187755</v>
+        <v>-2690.107701387755</v>
       </c>
       <c r="O86">
-        <v>-530.8332244375511</v>
+        <v>-538.021540277551</v>
       </c>
       <c r="P86">
-        <v>-2123.332897750204</v>
+        <v>-2152.086161110204</v>
       </c>
       <c r="Q86">
-        <v>-1026.932897750204</v>
+        <v>-1055.686161110204</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2838340665115812</v>
+        <v>0.2997030042790199</v>
       </c>
       <c r="T86">
-        <v>4.894230942674025</v>
+        <v>5.220513005518961</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02417458306712121</v>
+        <v>0.02389017620750802</v>
       </c>
       <c r="W86">
-        <v>0.2300996333127728</v>
+        <v>0.2301666964502696</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1208729153356061</v>
+        <v>0.1194508810375401</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2405971426245822</v>
+        <v>0.2424971426245822</v>
       </c>
       <c r="C87">
-        <v>-9256.433006003741</v>
+        <v>-9434.660549567565</v>
       </c>
       <c r="D87">
-        <v>2671.306993996258</v>
+        <v>2645.503450432436</v>
       </c>
       <c r="E87">
-        <v>7357.139999999999</v>
+        <v>7509.564</v>
       </c>
       <c r="F87">
-        <v>12956.04</v>
+        <v>13108.464</v>
       </c>
       <c r="G87">
         <v>1028.3</v>
@@ -8427,37 +8427,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M87">
-        <v>3055.034232</v>
+        <v>3090.9758112</v>
       </c>
       <c r="N87">
-        <v>-2690.107701387755</v>
+        <v>-2726.049280587755</v>
       </c>
       <c r="O87">
-        <v>-538.021540277551</v>
+        <v>-545.2098561175511</v>
       </c>
       <c r="P87">
-        <v>-2152.086161110204</v>
+        <v>-2180.839424470204</v>
       </c>
       <c r="Q87">
-        <v>-1055.686161110204</v>
+        <v>-1084.439424470204</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2997030042790199</v>
+        <v>0.3178389331560928</v>
       </c>
       <c r="T87">
-        <v>5.220513005518961</v>
+        <v>5.593406791627459</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02389017620750802</v>
+        <v>0.02361238346090909</v>
       </c>
       <c r="W87">
-        <v>0.2301666964502696</v>
+        <v>0.2302321999799176</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1194508810375401</v>
+        <v>0.1180619173045455</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2424971426245822</v>
+        <v>0.2443971426245821</v>
       </c>
       <c r="C88">
-        <v>-9434.660549567565</v>
+        <v>-9612.39436263634</v>
       </c>
       <c r="D88">
-        <v>2645.503450432436</v>
+        <v>2620.193637363658</v>
       </c>
       <c r="E88">
-        <v>7509.564</v>
+        <v>7661.987999999999</v>
       </c>
       <c r="F88">
-        <v>13108.464</v>
+        <v>13260.888</v>
       </c>
       <c r="G88">
         <v>1028.3</v>
@@ -8509,37 +8509,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M88">
-        <v>3090.9758112</v>
+        <v>3126.9173904</v>
       </c>
       <c r="N88">
-        <v>-2726.049280587755</v>
+        <v>-2761.990859787755</v>
       </c>
       <c r="O88">
-        <v>-545.2098561175511</v>
+        <v>-552.3981719575511</v>
       </c>
       <c r="P88">
-        <v>-2180.839424470204</v>
+        <v>-2209.592687830204</v>
       </c>
       <c r="Q88">
-        <v>-1084.439424470204</v>
+        <v>-1113.192687830204</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3178389331560928</v>
+        <v>0.3387650049373307</v>
       </c>
       <c r="T88">
-        <v>5.593406791627459</v>
+        <v>6.023668852521878</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02361238346090909</v>
+        <v>0.02334097675446186</v>
       </c>
       <c r="W88">
-        <v>0.2302321999799176</v>
+        <v>0.2302961976812979</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1180619173045455</v>
+        <v>0.1167048837723094</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2443971426245821</v>
+        <v>0.2462971426245822</v>
       </c>
       <c r="C89">
-        <v>-9612.39436263634</v>
+        <v>-9789.648481638649</v>
       </c>
       <c r="D89">
-        <v>2620.193637363658</v>
+        <v>2595.363518361351</v>
       </c>
       <c r="E89">
-        <v>7661.987999999999</v>
+        <v>7814.412</v>
       </c>
       <c r="F89">
-        <v>13260.888</v>
+        <v>13413.312</v>
       </c>
       <c r="G89">
         <v>1028.3</v>
@@ -8591,37 +8591,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M89">
-        <v>3126.9173904</v>
+        <v>3162.8589696</v>
       </c>
       <c r="N89">
-        <v>-2761.990859787755</v>
+        <v>-2797.932438987755</v>
       </c>
       <c r="O89">
-        <v>-552.3981719575511</v>
+        <v>-559.5864877975511</v>
       </c>
       <c r="P89">
-        <v>-2209.592687830204</v>
+        <v>-2238.345951190204</v>
       </c>
       <c r="Q89">
-        <v>-1113.192687830204</v>
+        <v>-1141.945951190204</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3387650049373307</v>
+        <v>0.3631787553487749</v>
       </c>
       <c r="T89">
-        <v>6.023668852521878</v>
+        <v>6.525641256898702</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02334097675446186</v>
+        <v>0.02307573838225207</v>
       </c>
       <c r="W89">
-        <v>0.2302961976812979</v>
+        <v>0.230358740889465</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1167048837723094</v>
+        <v>0.1153786919112604</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2462971426245822</v>
+        <v>0.2481971426245822</v>
       </c>
       <c r="C90">
-        <v>-9789.648481638649</v>
+        <v>-9966.436415936048</v>
       </c>
       <c r="D90">
-        <v>2595.363518361351</v>
+        <v>2570.999584063952</v>
       </c>
       <c r="E90">
-        <v>7814.412</v>
+        <v>7966.836000000001</v>
       </c>
       <c r="F90">
-        <v>13413.312</v>
+        <v>13565.736</v>
       </c>
       <c r="G90">
         <v>1028.3</v>
@@ -8673,37 +8673,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M90">
-        <v>3162.8589696</v>
+        <v>3198.8005488</v>
       </c>
       <c r="N90">
-        <v>-2797.932438987755</v>
+        <v>-2833.874018187756</v>
       </c>
       <c r="O90">
-        <v>-559.5864877975511</v>
+        <v>-566.7748036375511</v>
       </c>
       <c r="P90">
-        <v>-2238.345951190204</v>
+        <v>-2267.099214550205</v>
       </c>
       <c r="Q90">
-        <v>-1141.945951190204</v>
+        <v>-1170.699214550204</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3631787553487749</v>
+        <v>0.3920313694713909</v>
       </c>
       <c r="T90">
-        <v>6.525641256898702</v>
+        <v>7.118881371162221</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02307573838225207</v>
+        <v>0.02281646042290092</v>
       </c>
       <c r="W90">
-        <v>0.230358740889465</v>
+        <v>0.23041987863228</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1153786919112604</v>
+        <v>0.1140823021145045</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2481971426245822</v>
+        <v>0.2500971426245822</v>
       </c>
       <c r="C91">
-        <v>-9966.436415936048</v>
+        <v>-10142.77117233218</v>
       </c>
       <c r="D91">
-        <v>2570.999584063952</v>
+        <v>2547.088827667824</v>
       </c>
       <c r="E91">
-        <v>7966.836000000001</v>
+        <v>8119.26</v>
       </c>
       <c r="F91">
-        <v>13565.736</v>
+        <v>13718.16</v>
       </c>
       <c r="G91">
         <v>1028.3</v>
@@ -8755,37 +8755,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M91">
-        <v>3198.8005488</v>
+        <v>3234.742128</v>
       </c>
       <c r="N91">
-        <v>-2833.874018187756</v>
+        <v>-2869.815597387756</v>
       </c>
       <c r="O91">
-        <v>-566.7748036375511</v>
+        <v>-573.9631194775511</v>
       </c>
       <c r="P91">
-        <v>-2267.099214550205</v>
+        <v>-2295.852477910204</v>
       </c>
       <c r="Q91">
-        <v>-1170.699214550204</v>
+        <v>-1199.452477910204</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3920313694713909</v>
+        <v>0.42665450641853</v>
       </c>
       <c r="T91">
-        <v>7.118881371162221</v>
+        <v>7.830769508278443</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02281646042290092</v>
+        <v>0.0225629441959798</v>
       </c>
       <c r="W91">
-        <v>0.23041987863228</v>
+        <v>0.230479657758588</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1140823021145045</v>
+        <v>0.112814720979899</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2500971426245822</v>
+        <v>0.2519971426245822</v>
       </c>
       <c r="C92">
-        <v>-10142.77117233218</v>
+        <v>-10318.66527822681</v>
       </c>
       <c r="D92">
-        <v>2547.088827667824</v>
+        <v>2523.618721773195</v>
       </c>
       <c r="E92">
-        <v>8119.26</v>
+        <v>8271.684000000001</v>
       </c>
       <c r="F92">
-        <v>13718.16</v>
+        <v>13870.584</v>
       </c>
       <c r="G92">
         <v>1028.3</v>
@@ -8837,37 +8837,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M92">
-        <v>3234.742128</v>
+        <v>3270.6837072</v>
       </c>
       <c r="N92">
-        <v>-2869.815597387756</v>
+        <v>-2905.757176587756</v>
       </c>
       <c r="O92">
-        <v>-573.9631194775511</v>
+        <v>-581.1514353175511</v>
       </c>
       <c r="P92">
-        <v>-2295.852477910204</v>
+        <v>-2324.605741270204</v>
       </c>
       <c r="Q92">
-        <v>-1199.452477910204</v>
+        <v>-1228.205741270204</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.42665450641853</v>
+        <v>0.4689716737983667</v>
       </c>
       <c r="T92">
-        <v>7.830769508278443</v>
+        <v>8.700855009198271</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0225629441959798</v>
+        <v>0.02231499975426574</v>
       </c>
       <c r="W92">
-        <v>0.230479657758588</v>
+        <v>0.2305381230579441</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.112814720979899</v>
+        <v>0.1115749987713287</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2519971426245822</v>
+        <v>0.2538971426245822</v>
       </c>
       <c r="C93">
-        <v>-10318.66527822681</v>
+        <v>-10494.13080350147</v>
       </c>
       <c r="D93">
-        <v>2523.618721773195</v>
+        <v>2500.577196498533</v>
       </c>
       <c r="E93">
-        <v>8271.684000000001</v>
+        <v>8424.108</v>
       </c>
       <c r="F93">
-        <v>13870.584</v>
+        <v>14023.008</v>
       </c>
       <c r="G93">
         <v>1028.3</v>
@@ -8919,37 +8919,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M93">
-        <v>3270.6837072</v>
+        <v>3306.6252864</v>
       </c>
       <c r="N93">
-        <v>-2905.757176587756</v>
+        <v>-2941.698755787756</v>
       </c>
       <c r="O93">
-        <v>-581.1514353175511</v>
+        <v>-588.3397511575512</v>
       </c>
       <c r="P93">
-        <v>-2324.605741270204</v>
+        <v>-2353.359004630204</v>
       </c>
       <c r="Q93">
-        <v>-1228.205741270204</v>
+        <v>-1256.959004630204</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4689716737983667</v>
+        <v>0.5218681330231626</v>
       </c>
       <c r="T93">
-        <v>8.700855009198271</v>
+        <v>9.788461885348058</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02231499975426574</v>
+        <v>0.02207244540911067</v>
       </c>
       <c r="W93">
-        <v>0.2305381230579441</v>
+        <v>0.2305953173725317</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1115749987713287</v>
+        <v>0.1103622270455533</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2538971426245822</v>
+        <v>0.2557971426245822</v>
       </c>
       <c r="C94">
-        <v>-10494.13080350147</v>
+        <v>-10669.17938121699</v>
       </c>
       <c r="D94">
-        <v>2500.577196498533</v>
+        <v>2477.952618783012</v>
       </c>
       <c r="E94">
-        <v>8424.108</v>
+        <v>8576.532000000001</v>
       </c>
       <c r="F94">
-        <v>14023.008</v>
+        <v>14175.432</v>
       </c>
       <c r="G94">
         <v>1028.3</v>
@@ -9001,37 +9001,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M94">
-        <v>3306.6252864</v>
+        <v>3342.5668656</v>
       </c>
       <c r="N94">
-        <v>-2941.698755787756</v>
+        <v>-2977.640334987756</v>
       </c>
       <c r="O94">
-        <v>-588.3397511575512</v>
+        <v>-595.5280669975512</v>
       </c>
       <c r="P94">
-        <v>-2353.359004630204</v>
+        <v>-2382.112267990205</v>
       </c>
       <c r="Q94">
-        <v>-1256.959004630204</v>
+        <v>-1285.712267990205</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5218681330231626</v>
+        <v>0.5898778663121859</v>
       </c>
       <c r="T94">
-        <v>9.788461885348058</v>
+        <v>11.18681358325492</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02207244540911067</v>
+        <v>0.02183510728643206</v>
       </c>
       <c r="W94">
-        <v>0.2305953173725317</v>
+        <v>0.2306512817018593</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1103622270455533</v>
+        <v>0.1091755364321603</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2557971426245822</v>
+        <v>0.2576971426245822</v>
       </c>
       <c r="C95">
-        <v>-10669.17938121699</v>
+        <v>-10843.82222719751</v>
       </c>
       <c r="D95">
-        <v>2477.952618783012</v>
+        <v>2455.733772802493</v>
       </c>
       <c r="E95">
-        <v>8576.532000000001</v>
+        <v>8728.956</v>
       </c>
       <c r="F95">
-        <v>14175.432</v>
+        <v>14327.856</v>
       </c>
       <c r="G95">
         <v>1028.3</v>
@@ -9083,37 +9083,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M95">
-        <v>3342.5668656</v>
+        <v>3378.5084448</v>
       </c>
       <c r="N95">
-        <v>-2977.640334987756</v>
+        <v>-3013.581914187756</v>
       </c>
       <c r="O95">
-        <v>-595.5280669975512</v>
+        <v>-602.7163828375511</v>
       </c>
       <c r="P95">
-        <v>-2382.112267990205</v>
+        <v>-2410.865531350204</v>
       </c>
       <c r="Q95">
-        <v>-1285.712267990205</v>
+        <v>-1314.465531350204</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5898778663121859</v>
+        <v>0.6805575106975503</v>
       </c>
       <c r="T95">
-        <v>11.18681358325492</v>
+        <v>13.05128251379741</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02183510728643206</v>
+        <v>0.02160281891104449</v>
       </c>
       <c r="W95">
-        <v>0.2306512817018593</v>
+        <v>0.2307060553007757</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1091755364321603</v>
+        <v>0.1080140945552225</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2576971426245822</v>
+        <v>0.2595971426245822</v>
       </c>
       <c r="C96">
-        <v>-10843.82222719751</v>
+        <v>-11018.07015857024</v>
       </c>
       <c r="D96">
-        <v>2455.733772802493</v>
+        <v>2433.909841429762</v>
       </c>
       <c r="E96">
-        <v>8728.956</v>
+        <v>8881.380000000001</v>
       </c>
       <c r="F96">
-        <v>14327.856</v>
+        <v>14480.28</v>
       </c>
       <c r="G96">
         <v>1028.3</v>
@@ -9165,37 +9165,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M96">
-        <v>3378.5084448</v>
+        <v>3414.450024</v>
       </c>
       <c r="N96">
-        <v>-3013.581914187756</v>
+        <v>-3049.523493387755</v>
       </c>
       <c r="O96">
-        <v>-602.7163828375511</v>
+        <v>-609.9046986775511</v>
       </c>
       <c r="P96">
-        <v>-2410.865531350204</v>
+        <v>-2439.618794710204</v>
       </c>
       <c r="Q96">
-        <v>-1314.465531350204</v>
+        <v>-1343.218794710204</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6805575106975503</v>
+        <v>0.807509012837061</v>
       </c>
       <c r="T96">
-        <v>13.05128251379741</v>
+        <v>15.66153901655691</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02160281891104449</v>
+        <v>0.02137542081724402</v>
       </c>
       <c r="W96">
-        <v>0.2307060553007757</v>
+        <v>0.2307596757712939</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1080140945552225</v>
+        <v>0.1068771040862201</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2595971426245822</v>
+        <v>0.2614971426245822</v>
       </c>
       <c r="C97">
-        <v>-11018.07015857024</v>
+        <v>-11191.93361132537</v>
       </c>
       <c r="D97">
-        <v>2433.909841429762</v>
+        <v>2412.470388674632</v>
       </c>
       <c r="E97">
-        <v>8881.380000000001</v>
+        <v>9033.804000000002</v>
       </c>
       <c r="F97">
-        <v>14480.28</v>
+        <v>14632.704</v>
       </c>
       <c r="G97">
         <v>1028.3</v>
@@ -9247,37 +9247,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M97">
-        <v>3414.450024</v>
+        <v>3450.391603200001</v>
       </c>
       <c r="N97">
-        <v>-3049.523493387755</v>
+        <v>-3085.465072587756</v>
       </c>
       <c r="O97">
-        <v>-609.9046986775511</v>
+        <v>-617.0930145175512</v>
       </c>
       <c r="P97">
-        <v>-2439.618794710204</v>
+        <v>-2468.372058070205</v>
       </c>
       <c r="Q97">
-        <v>-1343.218794710204</v>
+        <v>-1371.972058070205</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.807509012837061</v>
+        <v>0.9979362660463265</v>
       </c>
       <c r="T97">
-        <v>15.66153901655691</v>
+        <v>19.57692377069614</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02137542081724402</v>
+        <v>0.02115276018373106</v>
       </c>
       <c r="W97">
-        <v>0.2307596757712939</v>
+        <v>0.2308121791486762</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1068771040862201</v>
+        <v>0.1057638009186553</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2614971426245822</v>
+        <v>0.2633971426245821</v>
       </c>
       <c r="C98">
-        <v>-11191.93361132537</v>
+        <v>-11365.422656956</v>
       </c>
       <c r="D98">
-        <v>2412.470388674632</v>
+        <v>2391.405343044001</v>
       </c>
       <c r="E98">
-        <v>9033.804</v>
+        <v>9186.227999999999</v>
       </c>
       <c r="F98">
-        <v>14632.704</v>
+        <v>14785.128</v>
       </c>
       <c r="G98">
         <v>1028.3</v>
@@ -9329,37 +9329,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M98">
-        <v>3450.3916032</v>
+        <v>3486.3331824</v>
       </c>
       <c r="N98">
-        <v>-3085.465072587755</v>
+        <v>-3121.406651787755</v>
       </c>
       <c r="O98">
-        <v>-617.0930145175512</v>
+        <v>-624.281330357551</v>
       </c>
       <c r="P98">
-        <v>-2468.372058070204</v>
+        <v>-2497.125321430204</v>
       </c>
       <c r="Q98">
-        <v>-1371.972058070204</v>
+        <v>-1400.725321430204</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9979362660463239</v>
+        <v>1.315315021395099</v>
       </c>
       <c r="T98">
-        <v>19.57692377069609</v>
+        <v>26.10256502759478</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02115276018373106</v>
+        <v>0.02093469049111528</v>
       </c>
       <c r="W98">
-        <v>0.2308121791486762</v>
+        <v>0.230863599982195</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1057638009186553</v>
+        <v>0.1046734524555764</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2633971426245821</v>
+        <v>0.2652971426245822</v>
       </c>
       <c r="C99">
-        <v>-11365.422656956</v>
+        <v>-11538.54701823385</v>
       </c>
       <c r="D99">
-        <v>2391.405343044001</v>
+        <v>2370.704981766154</v>
       </c>
       <c r="E99">
-        <v>9186.227999999999</v>
+        <v>9338.652</v>
       </c>
       <c r="F99">
-        <v>14785.128</v>
+        <v>14937.552</v>
       </c>
       <c r="G99">
         <v>1028.3</v>
@@ -9411,37 +9411,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M99">
-        <v>3486.3331824</v>
+        <v>3522.2747616</v>
       </c>
       <c r="N99">
-        <v>-3121.406651787755</v>
+        <v>-3157.348230987755</v>
       </c>
       <c r="O99">
-        <v>-624.281330357551</v>
+        <v>-631.4696461975511</v>
       </c>
       <c r="P99">
-        <v>-2497.125321430204</v>
+        <v>-2525.878584790205</v>
       </c>
       <c r="Q99">
-        <v>-1400.725321430204</v>
+        <v>-1429.478584790204</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.315315021395099</v>
+        <v>1.950072532092648</v>
       </c>
       <c r="T99">
-        <v>26.10256502759478</v>
+        <v>39.15384754139217</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02093469049111528</v>
+        <v>0.02072107120038962</v>
       </c>
       <c r="W99">
-        <v>0.230863599982195</v>
+        <v>0.2309139714109482</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1046734524555764</v>
+        <v>0.1036053560019481</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2652971426245822</v>
+        <v>0.2671971426245821</v>
       </c>
       <c r="C100">
-        <v>-11538.54701823385</v>
+        <v>-11711.31608417263</v>
       </c>
       <c r="D100">
-        <v>2370.704981766154</v>
+        <v>2350.35991582737</v>
       </c>
       <c r="E100">
-        <v>9338.652</v>
+        <v>9491.075999999999</v>
       </c>
       <c r="F100">
-        <v>14937.552</v>
+        <v>15089.976</v>
       </c>
       <c r="G100">
         <v>1028.3</v>
@@ -9493,37 +9493,37 @@
         <v>364.9265306122447</v>
       </c>
       <c r="M100">
-        <v>3522.2747616</v>
+        <v>3558.2163408</v>
       </c>
       <c r="N100">
-        <v>-3157.348230987755</v>
+        <v>-3193.289810187755</v>
       </c>
       <c r="O100">
-        <v>-631.4696461975511</v>
+        <v>-638.657962037551</v>
       </c>
       <c r="P100">
-        <v>-2525.878584790205</v>
+        <v>-2554.631848150204</v>
       </c>
       <c r="Q100">
-        <v>-1429.478584790204</v>
+        <v>-1458.231848150204</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.950072532092648</v>
+        <v>3.854345064185296</v>
       </c>
       <c r="T100">
-        <v>39.15384754139217</v>
+        <v>78.30769508278435</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02072107120038962</v>
+        <v>0.02051176745089073</v>
       </c>
       <c r="W100">
-        <v>0.2309139714109482</v>
+        <v>0.23096332523508</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1036053560019481</v>
+        <v>0.1025588372544537</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2671971426245821</v>
-      </c>
-      <c r="C101">
-        <v>-11711.31608417263</v>
-      </c>
-      <c r="D101">
-        <v>2350.35991582737</v>
-      </c>
-      <c r="E101">
-        <v>9491.075999999999</v>
-      </c>
-      <c r="F101">
-        <v>15089.976</v>
-      </c>
-      <c r="G101">
-        <v>1028.3</v>
-      </c>
-      <c r="H101">
-        <v>9643.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1461.326530612245</v>
-      </c>
-      <c r="K101">
-        <v>1096.4</v>
-      </c>
-      <c r="L101">
-        <v>364.9265306122447</v>
-      </c>
-      <c r="M101">
-        <v>3558.2163408</v>
-      </c>
-      <c r="N101">
-        <v>-3193.289810187755</v>
-      </c>
-      <c r="O101">
-        <v>-638.657962037551</v>
-      </c>
-      <c r="P101">
-        <v>-2554.631848150204</v>
-      </c>
-      <c r="Q101">
-        <v>-1458.231848150204</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.854345064185296</v>
-      </c>
-      <c r="T101">
-        <v>78.30769508278435</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02051176745089073</v>
-      </c>
-      <c r="W101">
-        <v>0.23096332523508</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1025588372544537</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
